--- a/8_Galar_Data.xlsx
+++ b/8_Galar_Data.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>Ok</v>
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>Ok</v>
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>Ok</v>
@@ -574,7 +574,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>Ok</v>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>Ok</v>
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>Ok</v>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>Ok</v>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>Ok</v>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>Ok</v>
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>Ok</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>Ok</v>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>Ok</v>
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>Ok</v>
@@ -954,7 +954,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>Ok</v>
@@ -992,7 +992,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>Ok</v>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>Ok</v>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>Ok</v>
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Ok</v>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>Ok</v>
@@ -1182,7 +1182,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>Ok</v>
@@ -1220,7 +1220,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>Ok</v>
@@ -1258,7 +1258,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>Ok</v>
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>Ok</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>Ok</v>
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>Ok</v>
@@ -1410,7 +1410,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>Ok</v>
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>Ok</v>
@@ -1486,7 +1486,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>Ok</v>
@@ -1524,7 +1524,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>Ok</v>
@@ -1562,7 +1562,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>Ok</v>
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v>Ok</v>
@@ -1638,7 +1638,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v>Ok</v>
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v>Ok</v>
@@ -1714,7 +1714,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v>Ok</v>
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H36" t="str">
         <v>Ok</v>
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H37" t="str">
         <v>Ok</v>
@@ -1828,7 +1828,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H38" t="str">
         <v>Ok</v>
@@ -1866,7 +1866,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v>Ok</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>Ok</v>
@@ -1942,7 +1942,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>Ok</v>
@@ -1980,7 +1980,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v>Ok</v>
@@ -2018,7 +2018,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>Ok</v>
@@ -2056,7 +2056,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H44" t="str">
         <v>Ok</v>
@@ -2094,7 +2094,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H45" t="str">
         <v>Ok</v>
@@ -2132,7 +2132,7 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H46" t="str">
         <v>Ok</v>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v>Ok</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H48" t="str">
         <v>Ok</v>
@@ -2246,7 +2246,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>Ok</v>
@@ -2284,7 +2284,7 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v>Ok</v>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>Ok</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v>Ok</v>
@@ -2398,7 +2398,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>Ok</v>
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>Ok</v>
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v>Ok</v>
@@ -2512,7 +2512,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v>Ok</v>
@@ -2550,7 +2550,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v>Ok</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v>Ok</v>
@@ -2626,7 +2626,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>Ok</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v>Ok</v>
@@ -2702,7 +2702,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v>Ok</v>
@@ -2740,7 +2740,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H62" t="str">
         <v>Ok</v>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H63" t="str">
         <v>Ok</v>
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H64" t="str">
         <v>Ok</v>
@@ -2854,7 +2854,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H65" t="str">
         <v>Ok</v>
@@ -2892,7 +2892,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v>Ok</v>
@@ -2930,7 +2930,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H67" t="str">
         <v>Ok</v>
@@ -2968,7 +2968,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H68" t="str">
         <v>Ok</v>
@@ -3006,7 +3006,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v>Ok</v>
@@ -3044,7 +3044,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H70" t="str">
         <v>Ok</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H71" t="str">
         <v>Ok</v>
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H72" t="str">
         <v>Ok</v>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H73" t="str">
         <v>Ok</v>
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H74" t="str">
         <v>Ok</v>
@@ -3234,7 +3234,7 @@
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H75" t="str">
         <v>Ok</v>
@@ -3272,7 +3272,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H76" t="str">
         <v>Ok</v>
@@ -3310,7 +3310,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v>Ok</v>
@@ -3348,7 +3348,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H78" t="str">
         <v>Ok</v>
@@ -3386,7 +3386,7 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H79" t="str">
         <v>Ok</v>
@@ -3424,7 +3424,7 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H80" t="str">
         <v>Ok</v>
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H81" t="str">
         <v>Ok</v>
@@ -3500,7 +3500,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H82" t="str">
         <v>Ok</v>
@@ -3538,7 +3538,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H83" t="str">
         <v>Ok</v>
@@ -3576,7 +3576,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H84" t="str">
         <v>Ok</v>
@@ -3614,7 +3614,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H85" t="str">
         <v>Ok</v>
@@ -3652,7 +3652,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H86" t="str">
         <v>Ok</v>
@@ -3690,7 +3690,7 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H87" t="str">
         <v>Ok</v>
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H88" t="str">
         <v>Ok</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H89" t="str">
         <v>Ok</v>
@@ -3804,7 +3804,7 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H90" t="str">
         <v>Ok</v>
@@ -3842,7 +3842,7 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H91" t="str">
         <v>Ok</v>
@@ -3880,7 +3880,7 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H92" t="str">
         <v>Ok</v>
@@ -3918,7 +3918,7 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v>Ok</v>
@@ -3956,7 +3956,7 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H94" t="str">
         <v>Ok</v>
@@ -3994,7 +3994,7 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H95" t="str">
         <v>Ok</v>
@@ -4032,7 +4032,7 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H96" t="str">
         <v>Ok</v>
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H97" t="str">
         <v>Ok</v>
@@ -4108,7 +4108,7 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H98" t="str">
         <v>Ok</v>
@@ -4146,7 +4146,7 @@
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H99" t="str">
         <v>Ok</v>
@@ -4184,7 +4184,7 @@
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H100" t="str">
         <v>Ok</v>
@@ -4222,7 +4222,7 @@
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H101" t="str">
         <v>Ok</v>
@@ -4260,7 +4260,7 @@
         <v/>
       </c>
       <c r="G102" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H102" t="str">
         <v>Ok</v>
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H103" t="str">
         <v>Ok</v>
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H104" t="str">
         <v>Ok</v>
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H105" t="str">
         <v>Ok</v>
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H106" t="str">
         <v>NONONO</v>
@@ -4450,7 +4450,7 @@
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H107" t="str">
         <v>Ok</v>
@@ -4488,7 +4488,7 @@
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H108" t="str">
         <v>Ok</v>
@@ -4526,7 +4526,7 @@
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H109" t="str">
         <v>Ok</v>
@@ -4564,7 +4564,7 @@
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H110" t="str">
         <v>Ok</v>
@@ -4602,7 +4602,7 @@
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H111" t="str">
         <v>Ok</v>
@@ -4640,7 +4640,7 @@
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H112" t="str">
         <v>Ok</v>
@@ -4678,7 +4678,7 @@
         <v/>
       </c>
       <c r="G113" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H113" t="str">
         <v>Ok</v>
@@ -4716,7 +4716,7 @@
         <v/>
       </c>
       <c r="G114" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H114" t="str">
         <v>Ok</v>
@@ -4754,7 +4754,7 @@
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H115" t="str">
         <v>Ok</v>
@@ -4792,7 +4792,7 @@
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H116" t="str">
         <v>Ok</v>
@@ -4830,7 +4830,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H117" t="str">
         <v>Ok</v>
@@ -4868,7 +4868,7 @@
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H118" t="str">
         <v>Ok</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="G119" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H119" t="str">
         <v>Ok</v>
@@ -4944,7 +4944,7 @@
         <v/>
       </c>
       <c r="G120" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H120" t="str">
         <v>Ok</v>
@@ -4982,7 +4982,7 @@
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H121" t="str">
         <v>Ok</v>
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H122" t="str">
         <v>Ok</v>
@@ -5058,7 +5058,7 @@
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H123" t="str">
         <v>Ok</v>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H124" t="str">
         <v>Ok</v>
@@ -5134,7 +5134,7 @@
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H125" t="str">
         <v>Ok</v>
@@ -5172,7 +5172,7 @@
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H126" t="str">
         <v>Ok</v>
@@ -5210,7 +5210,7 @@
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H127" t="str">
         <v>Ok</v>
@@ -5248,7 +5248,7 @@
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H128" t="str">
         <v>Ok</v>
@@ -5286,7 +5286,7 @@
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H129" t="str">
         <v>Ok</v>
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H130" t="str">
         <v>Ok</v>
@@ -5362,7 +5362,7 @@
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H131" t="str">
         <v>NONONO</v>
@@ -5400,7 +5400,7 @@
         <v/>
       </c>
       <c r="G132" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H132" t="str">
         <v>Ok</v>
@@ -5438,7 +5438,7 @@
         <v/>
       </c>
       <c r="G133" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H133" t="str">
         <v>NONONO</v>
@@ -5476,7 +5476,7 @@
         <v/>
       </c>
       <c r="G134" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H134" t="str">
         <v>Ok</v>
@@ -5514,7 +5514,7 @@
         <v/>
       </c>
       <c r="G135" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H135" t="str">
         <v>Ok</v>
@@ -5552,7 +5552,7 @@
         <v/>
       </c>
       <c r="G136" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H136" t="str">
         <v>Ok</v>
@@ -5590,7 +5590,7 @@
         <v/>
       </c>
       <c r="G137" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H137" t="str">
         <v>Ok</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="G138" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H138" t="str">
         <v>Ok</v>
@@ -5666,7 +5666,7 @@
         <v/>
       </c>
       <c r="G139" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H139" t="str">
         <v>Ok</v>
@@ -5704,7 +5704,7 @@
         <v/>
       </c>
       <c r="G140" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H140" t="str">
         <v>Ok</v>
@@ -5742,7 +5742,7 @@
         <v/>
       </c>
       <c r="G141" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H141" t="str">
         <v>Ok</v>
@@ -5780,7 +5780,7 @@
         <v/>
       </c>
       <c r="G142" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H142" t="str">
         <v>Ok</v>
@@ -5818,7 +5818,7 @@
         <v/>
       </c>
       <c r="G143" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H143" t="str">
         <v>Ok</v>
@@ -5856,7 +5856,7 @@
         <v/>
       </c>
       <c r="G144" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H144" t="str">
         <v>Ok</v>
@@ -5894,7 +5894,7 @@
         <v/>
       </c>
       <c r="G145" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H145" t="str">
         <v>Ok</v>
@@ -5932,7 +5932,7 @@
         <v/>
       </c>
       <c r="G146" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H146" t="str">
         <v>Ok</v>
@@ -5970,7 +5970,7 @@
         <v/>
       </c>
       <c r="G147" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H147" t="str">
         <v>Ok</v>
@@ -6008,7 +6008,7 @@
         <v/>
       </c>
       <c r="G148" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H148" t="str">
         <v>Ok</v>
@@ -6046,7 +6046,7 @@
         <v/>
       </c>
       <c r="G149" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H149" t="str">
         <v>Ok</v>
@@ -6084,7 +6084,7 @@
         <v/>
       </c>
       <c r="G150" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H150" t="str">
         <v>Ok</v>
@@ -6122,7 +6122,7 @@
         <v/>
       </c>
       <c r="G151" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H151" t="str">
         <v>Ok</v>
@@ -6160,7 +6160,7 @@
         <v/>
       </c>
       <c r="G152" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H152" t="str">
         <v>Ok</v>
@@ -6198,7 +6198,7 @@
         <v/>
       </c>
       <c r="G153" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H153" t="str">
         <v>Ok</v>
@@ -6236,7 +6236,7 @@
         <v/>
       </c>
       <c r="G154" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H154" t="str">
         <v>Ok</v>
@@ -6274,7 +6274,7 @@
         <v/>
       </c>
       <c r="G155" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H155" t="str">
         <v>Ok</v>
@@ -6312,7 +6312,7 @@
         <v/>
       </c>
       <c r="G156" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H156" t="str">
         <v>NONONO</v>
@@ -6350,7 +6350,7 @@
         <v/>
       </c>
       <c r="G157" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H157" t="str">
         <v>Ok</v>
@@ -6388,7 +6388,7 @@
         <v/>
       </c>
       <c r="G158" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H158" t="str">
         <v>Ok</v>
@@ -6426,7 +6426,7 @@
         <v/>
       </c>
       <c r="G159" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H159" t="str">
         <v>Ok</v>
@@ -6464,7 +6464,7 @@
         <v/>
       </c>
       <c r="G160" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H160" t="str">
         <v>Ok</v>
@@ -6502,7 +6502,7 @@
         <v/>
       </c>
       <c r="G161" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H161" t="str">
         <v>NONONO</v>
@@ -6540,7 +6540,7 @@
         <v/>
       </c>
       <c r="G162" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H162" t="str">
         <v>NONONO</v>
@@ -6578,7 +6578,7 @@
         <v/>
       </c>
       <c r="G163" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H163" t="str">
         <v>NONONO</v>
@@ -6616,7 +6616,7 @@
         <v/>
       </c>
       <c r="G164" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H164" t="str">
         <v>NONONO</v>
@@ -6654,7 +6654,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H165" t="str">
         <v>Ok</v>
@@ -6692,7 +6692,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H166" t="str">
         <v>Ok</v>
@@ -6730,7 +6730,7 @@
         <v/>
       </c>
       <c r="G167" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H167" t="str">
         <v>Ok</v>
@@ -6768,7 +6768,7 @@
         <v/>
       </c>
       <c r="G168" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H168" t="str">
         <v>Ok</v>
@@ -6806,7 +6806,7 @@
         <v/>
       </c>
       <c r="G169" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H169" t="str">
         <v>Ok</v>
@@ -6844,7 +6844,7 @@
         <v/>
       </c>
       <c r="G170" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H170" t="str">
         <v>Ok</v>
@@ -6882,7 +6882,7 @@
         <v/>
       </c>
       <c r="G171" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H171" t="str">
         <v>Ok</v>
@@ -6920,7 +6920,7 @@
         <v/>
       </c>
       <c r="G172" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H172" t="str">
         <v>Ok</v>
@@ -6958,7 +6958,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H173" t="str">
         <v>Ok</v>
@@ -6996,7 +6996,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H174" t="str">
         <v>Ok</v>
@@ -7034,7 +7034,7 @@
         <v/>
       </c>
       <c r="G175" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H175" t="str">
         <v>Ok</v>
@@ -7072,7 +7072,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H176" t="str">
         <v>Ok</v>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="G177" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H177" t="str">
         <v>Ok</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="G178" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H178" t="str">
         <v>Ok</v>
@@ -7186,7 +7186,7 @@
         <v/>
       </c>
       <c r="G179" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H179" t="str">
         <v>Ok</v>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="G180" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H180" t="str">
         <v>Ok</v>
@@ -7262,7 +7262,7 @@
         <v/>
       </c>
       <c r="G181" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H181" t="str">
         <v>NONONO</v>
@@ -7300,7 +7300,7 @@
         <v/>
       </c>
       <c r="G182" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H182" t="str">
         <v>Ok</v>
@@ -7338,7 +7338,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H183" t="str">
         <v>Ok</v>
@@ -7376,7 +7376,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H184" t="str">
         <v>Ok</v>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H185" t="str">
         <v>Ok</v>
@@ -7452,7 +7452,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H186" t="str">
         <v>NONONO</v>
@@ -7490,7 +7490,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H187" t="str">
         <v>Ok</v>
@@ -7528,7 +7528,7 @@
         <v/>
       </c>
       <c r="G188" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H188" t="str">
         <v>Ok</v>
@@ -7566,7 +7566,7 @@
         <v/>
       </c>
       <c r="G189" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H189" t="str">
         <v>Ok</v>
@@ -7604,7 +7604,7 @@
         <v/>
       </c>
       <c r="G190" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H190" t="str">
         <v>Ok</v>
@@ -7642,7 +7642,7 @@
         <v/>
       </c>
       <c r="G191" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H191" t="str">
         <v>Ok</v>
@@ -7680,7 +7680,7 @@
         <v/>
       </c>
       <c r="G192" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H192" t="str">
         <v>Ok</v>
@@ -7718,7 +7718,7 @@
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H193" t="str">
         <v>Ok</v>
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="G194" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H194" t="str">
         <v>Ok</v>
@@ -7794,7 +7794,7 @@
         <v/>
       </c>
       <c r="G195" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H195" t="str">
         <v>Ok</v>
@@ -7832,7 +7832,7 @@
         <v/>
       </c>
       <c r="G196" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H196" t="str">
         <v>Ok</v>
@@ -7870,7 +7870,7 @@
         <v/>
       </c>
       <c r="G197" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H197" t="str">
         <v>Ok</v>
@@ -7908,7 +7908,7 @@
         <v/>
       </c>
       <c r="G198" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H198" t="str">
         <v>Ok</v>
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H199" t="str">
         <v>Ok</v>
@@ -7984,7 +7984,7 @@
         <v/>
       </c>
       <c r="G200" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H200" t="str">
         <v>Ok</v>
@@ -8022,7 +8022,7 @@
         <v/>
       </c>
       <c r="G201" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H201" t="str">
         <v>Ok</v>
@@ -8060,7 +8060,7 @@
         <v/>
       </c>
       <c r="G202" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H202" t="str">
         <v>Ok</v>
@@ -8098,7 +8098,7 @@
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H203" t="str">
         <v>Ok</v>
@@ -8136,7 +8136,7 @@
         <v/>
       </c>
       <c r="G204" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H204" t="str">
         <v>Ok</v>
@@ -8174,7 +8174,7 @@
         <v/>
       </c>
       <c r="G205" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H205" t="str">
         <v>Ok</v>
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="G206" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H206" t="str">
         <v>Ok</v>
@@ -8250,7 +8250,7 @@
         <v/>
       </c>
       <c r="G207" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H207" t="str">
         <v>Ok</v>
@@ -8288,7 +8288,7 @@
         <v/>
       </c>
       <c r="G208" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H208" t="str">
         <v>Ok</v>
@@ -8326,7 +8326,7 @@
         <v/>
       </c>
       <c r="G209" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H209" t="str">
         <v>Ok</v>
@@ -8364,7 +8364,7 @@
         <v/>
       </c>
       <c r="G210" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H210" t="str">
         <v>Ok</v>
@@ -8402,7 +8402,7 @@
         <v/>
       </c>
       <c r="G211" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H211" t="str">
         <v>Ok</v>
@@ -8440,7 +8440,7 @@
         <v/>
       </c>
       <c r="G212" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H212" t="str">
         <v>Ok</v>
@@ -8478,7 +8478,7 @@
         <v/>
       </c>
       <c r="G213" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H213" t="str">
         <v>Ok</v>
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="G214" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H214" t="str">
         <v>Ok</v>
@@ -8554,7 +8554,7 @@
         <v/>
       </c>
       <c r="G215" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H215" t="str">
         <v>Ok</v>
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H216" t="str">
         <v>Ok</v>
@@ -8630,7 +8630,7 @@
         <v/>
       </c>
       <c r="G217" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H217" t="str">
         <v>Ok</v>
@@ -8668,7 +8668,7 @@
         <v/>
       </c>
       <c r="G218" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H218" t="str">
         <v>Ok</v>
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="G219" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H219" t="str">
         <v>Ok</v>
@@ -8744,7 +8744,7 @@
         <v/>
       </c>
       <c r="G220" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H220" t="str">
         <v>Ok</v>
@@ -8782,7 +8782,7 @@
         <v/>
       </c>
       <c r="G221" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H221" t="str">
         <v>NONONO</v>
@@ -8820,7 +8820,7 @@
         <v/>
       </c>
       <c r="G222" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H222" t="str">
         <v>Ok</v>
@@ -8858,7 +8858,7 @@
         <v/>
       </c>
       <c r="G223" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H223" t="str">
         <v>Ok</v>
@@ -8896,7 +8896,7 @@
         <v/>
       </c>
       <c r="G224" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H224" t="str">
         <v>Ok</v>
@@ -8934,7 +8934,7 @@
         <v/>
       </c>
       <c r="G225" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H225" t="str">
         <v>NONONO</v>
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="G226" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H226" t="str">
         <v>Ok</v>
@@ -9010,7 +9010,7 @@
         <v/>
       </c>
       <c r="G227" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H227" t="str">
         <v>Ok</v>
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H228" t="str">
         <v>Ok</v>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="G229" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H229" t="str">
         <v>Ok</v>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="G230" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H230" t="str">
         <v>NONONO</v>
@@ -9162,7 +9162,7 @@
         <v/>
       </c>
       <c r="G231" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H231" t="str">
         <v>Ok</v>
@@ -9200,7 +9200,7 @@
         <v/>
       </c>
       <c r="G232" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H232" t="str">
         <v>NONONO</v>
@@ -9238,7 +9238,7 @@
         <v/>
       </c>
       <c r="G233" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H233" t="str">
         <v>Ok</v>
@@ -9276,7 +9276,7 @@
         <v/>
       </c>
       <c r="G234" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H234" t="str">
         <v>Ok</v>
@@ -9314,7 +9314,7 @@
         <v/>
       </c>
       <c r="G235" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H235" t="str">
         <v>Ok</v>
@@ -9352,7 +9352,7 @@
         <v/>
       </c>
       <c r="G236" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H236" t="str">
         <v>Ok</v>
@@ -9390,7 +9390,7 @@
         <v/>
       </c>
       <c r="G237" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H237" t="str">
         <v>Ok</v>
@@ -9428,7 +9428,7 @@
         <v/>
       </c>
       <c r="G238" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H238" t="str">
         <v>Ok</v>
@@ -9466,7 +9466,7 @@
         <v/>
       </c>
       <c r="G239" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H239" t="str">
         <v>Ok</v>
@@ -9504,7 +9504,7 @@
         <v/>
       </c>
       <c r="G240" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H240" t="str">
         <v>Ok</v>
@@ -9542,7 +9542,7 @@
         <v/>
       </c>
       <c r="G241" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H241" t="str">
         <v>Ok</v>
@@ -9580,7 +9580,7 @@
         <v/>
       </c>
       <c r="G242" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H242" t="str">
         <v>Ok</v>
@@ -9618,7 +9618,7 @@
         <v/>
       </c>
       <c r="G243" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H243" t="str">
         <v>Ok</v>
@@ -9656,7 +9656,7 @@
         <v/>
       </c>
       <c r="G244" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H244" t="str">
         <v>Ok</v>
@@ -9694,7 +9694,7 @@
         <v/>
       </c>
       <c r="G245" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H245" t="str">
         <v>Ok</v>
@@ -9732,7 +9732,7 @@
         <v/>
       </c>
       <c r="G246" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H246" t="str">
         <v>Ok</v>
@@ -9770,7 +9770,7 @@
         <v/>
       </c>
       <c r="G247" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H247" t="str">
         <v>Ok</v>
@@ -9808,7 +9808,7 @@
         <v/>
       </c>
       <c r="G248" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H248" t="str">
         <v>Ok</v>
@@ -9846,7 +9846,7 @@
         <v/>
       </c>
       <c r="G249" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H249" t="str">
         <v>Ok</v>
@@ -9884,7 +9884,7 @@
         <v/>
       </c>
       <c r="G250" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H250" t="str">
         <v>Ok</v>
@@ -9922,7 +9922,7 @@
         <v/>
       </c>
       <c r="G251" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H251" t="str">
         <v>Ok</v>
@@ -9960,7 +9960,7 @@
         <v/>
       </c>
       <c r="G252" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H252" t="str">
         <v>Ok</v>
@@ -9998,7 +9998,7 @@
         <v/>
       </c>
       <c r="G253" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H253" t="str">
         <v>Ok</v>
@@ -10036,7 +10036,7 @@
         <v/>
       </c>
       <c r="G254" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H254" t="str">
         <v>Ok</v>
@@ -10074,7 +10074,7 @@
         <v/>
       </c>
       <c r="G255" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H255" t="str">
         <v>Ok</v>
@@ -10112,7 +10112,7 @@
         <v/>
       </c>
       <c r="G256" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H256" t="str">
         <v>Ok</v>
@@ -10150,7 +10150,7 @@
         <v/>
       </c>
       <c r="G257" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H257" t="str">
         <v>Ok</v>
@@ -10188,7 +10188,7 @@
         <v/>
       </c>
       <c r="G258" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H258" t="str">
         <v>Ok</v>
@@ -10226,7 +10226,7 @@
         <v/>
       </c>
       <c r="G259" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H259" t="str">
         <v>Ok</v>
@@ -10264,7 +10264,7 @@
         <v/>
       </c>
       <c r="G260" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H260" t="str">
         <v>Ok</v>
@@ -10302,7 +10302,7 @@
         <v/>
       </c>
       <c r="G261" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H261" t="str">
         <v>NONONO</v>
@@ -10340,7 +10340,7 @@
         <v/>
       </c>
       <c r="G262" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H262" t="str">
         <v>NONONO</v>
@@ -10378,7 +10378,7 @@
         <v/>
       </c>
       <c r="G263" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H263" t="str">
         <v>Ok</v>
@@ -10416,7 +10416,7 @@
         <v/>
       </c>
       <c r="G264" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H264" t="str">
         <v>NONONO</v>
@@ -10454,7 +10454,7 @@
         <v/>
       </c>
       <c r="G265" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H265" t="str">
         <v>NONONO</v>
@@ -10492,7 +10492,7 @@
         <v/>
       </c>
       <c r="G266" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H266" t="str">
         <v>Ok</v>
@@ -10530,7 +10530,7 @@
         <v/>
       </c>
       <c r="G267" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H267" t="str">
         <v>Ok</v>
@@ -10568,7 +10568,7 @@
         <v/>
       </c>
       <c r="G268" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H268" t="str">
         <v>Ok</v>
@@ -10606,7 +10606,7 @@
         <v/>
       </c>
       <c r="G269" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H269" t="str">
         <v>Ok</v>
@@ -10644,7 +10644,7 @@
         <v/>
       </c>
       <c r="G270" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H270" t="str">
         <v>NONONO</v>
@@ -10682,7 +10682,7 @@
         <v/>
       </c>
       <c r="G271" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H271" t="str">
         <v>Ok</v>
@@ -10720,7 +10720,7 @@
         <v/>
       </c>
       <c r="G272" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H272" t="str">
         <v>Ok</v>
@@ -10758,7 +10758,7 @@
         <v/>
       </c>
       <c r="G273" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H273" t="str">
         <v>Ok</v>
@@ -10796,7 +10796,7 @@
         <v/>
       </c>
       <c r="G274" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H274" t="str">
         <v>Ok</v>
@@ -10834,7 +10834,7 @@
         <v/>
       </c>
       <c r="G275" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H275" t="str">
         <v>Ok</v>
@@ -10872,7 +10872,7 @@
         <v/>
       </c>
       <c r="G276" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H276" t="str">
         <v>Ok</v>
@@ -10910,7 +10910,7 @@
         <v/>
       </c>
       <c r="G277" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H277" t="str">
         <v>NONONO</v>
@@ -10948,7 +10948,7 @@
         <v/>
       </c>
       <c r="G278" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H278" t="str">
         <v>Ok</v>
@@ -10986,7 +10986,7 @@
         <v/>
       </c>
       <c r="G279" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H279" t="str">
         <v>Ok</v>
@@ -11024,7 +11024,7 @@
         <v/>
       </c>
       <c r="G280" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H280" t="str">
         <v>Ok</v>
@@ -11062,7 +11062,7 @@
         <v/>
       </c>
       <c r="G281" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H281" t="str">
         <v>Ok</v>
@@ -11100,7 +11100,7 @@
         <v/>
       </c>
       <c r="G282" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H282" t="str">
         <v>Ok</v>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="G283" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H283" t="str">
         <v>Ok</v>
@@ -11176,7 +11176,7 @@
         <v/>
       </c>
       <c r="G284" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H284" t="str">
         <v>Ok</v>
@@ -11214,7 +11214,7 @@
         <v/>
       </c>
       <c r="G285" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H285" t="str">
         <v>Ok</v>
@@ -11252,7 +11252,7 @@
         <v/>
       </c>
       <c r="G286" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H286" t="str">
         <v>Ok</v>
@@ -11290,7 +11290,7 @@
         <v/>
       </c>
       <c r="G287" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H287" t="str">
         <v>Ok</v>
@@ -11328,7 +11328,7 @@
         <v/>
       </c>
       <c r="G288" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H288" t="str">
         <v>Ok</v>
@@ -11366,7 +11366,7 @@
         <v/>
       </c>
       <c r="G289" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H289" t="str">
         <v>Ok</v>
@@ -11404,7 +11404,7 @@
         <v/>
       </c>
       <c r="G290" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H290" t="str">
         <v>Ok</v>
@@ -11442,7 +11442,7 @@
         <v/>
       </c>
       <c r="G291" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H291" t="str">
         <v>Ok</v>
@@ -11480,7 +11480,7 @@
         <v/>
       </c>
       <c r="G292" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H292" t="str">
         <v>Ok</v>
@@ -11518,7 +11518,7 @@
         <v/>
       </c>
       <c r="G293" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H293" t="str">
         <v>Ok</v>
@@ -11556,7 +11556,7 @@
         <v/>
       </c>
       <c r="G294" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H294" t="str">
         <v>Ok</v>
@@ -11594,7 +11594,7 @@
         <v/>
       </c>
       <c r="G295" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H295" t="str">
         <v>Ok</v>
@@ -11632,7 +11632,7 @@
         <v/>
       </c>
       <c r="G296" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H296" t="str">
         <v>Ok</v>
@@ -11670,7 +11670,7 @@
         <v/>
       </c>
       <c r="G297" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H297" t="str">
         <v>Ok</v>
@@ -11708,7 +11708,7 @@
         <v/>
       </c>
       <c r="G298" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H298" t="str">
         <v>Ok</v>
@@ -11746,7 +11746,7 @@
         <v/>
       </c>
       <c r="G299" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H299" t="str">
         <v>Ok</v>
@@ -11784,7 +11784,7 @@
         <v/>
       </c>
       <c r="G300" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H300" t="str">
         <v>Ok</v>
@@ -11822,7 +11822,7 @@
         <v/>
       </c>
       <c r="G301" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H301" t="str">
         <v>Ok</v>
@@ -11860,7 +11860,7 @@
         <v/>
       </c>
       <c r="G302" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H302" t="str">
         <v>Ok</v>
@@ -11898,7 +11898,7 @@
         <v/>
       </c>
       <c r="G303" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H303" t="str">
         <v>NONONO</v>
@@ -11936,7 +11936,7 @@
         <v/>
       </c>
       <c r="G304" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H304" t="str">
         <v>NONONO</v>
@@ -11974,7 +11974,7 @@
         <v/>
       </c>
       <c r="G305" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H305" t="str">
         <v>Ok</v>
@@ -12012,7 +12012,7 @@
         <v/>
       </c>
       <c r="G306" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H306" t="str">
         <v>Ok</v>
@@ -12050,7 +12050,7 @@
         <v/>
       </c>
       <c r="G307" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H307" t="str">
         <v>Ok</v>
@@ -12088,7 +12088,7 @@
         <v/>
       </c>
       <c r="G308" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H308" t="str">
         <v>NONONO</v>
@@ -12126,7 +12126,7 @@
         <v/>
       </c>
       <c r="G309" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H309" t="str">
         <v>Ok</v>
@@ -12164,7 +12164,7 @@
         <v/>
       </c>
       <c r="G310" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H310" t="str">
         <v>Ok</v>
@@ -12202,7 +12202,7 @@
         <v/>
       </c>
       <c r="G311" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H311" t="str">
         <v>NONONO</v>
@@ -12240,7 +12240,7 @@
         <v/>
       </c>
       <c r="G312" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H312" t="str">
         <v>Ok</v>
@@ -12278,7 +12278,7 @@
         <v/>
       </c>
       <c r="G313" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H313" t="str">
         <v>Ok</v>
@@ -12316,7 +12316,7 @@
         <v/>
       </c>
       <c r="G314" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H314" t="str">
         <v>Ok</v>
@@ -12354,7 +12354,7 @@
         <v/>
       </c>
       <c r="G315" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H315" t="str">
         <v>Ok</v>
@@ -12392,7 +12392,7 @@
         <v/>
       </c>
       <c r="G316" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H316" t="str">
         <v>Ok</v>
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="G317" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H317" t="str">
         <v>Ok</v>
@@ -12468,7 +12468,7 @@
         <v/>
       </c>
       <c r="G318" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H318" t="str">
         <v>Ok</v>
@@ -12506,7 +12506,7 @@
         <v/>
       </c>
       <c r="G319" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H319" t="str">
         <v>Ok</v>
@@ -12544,7 +12544,7 @@
         <v/>
       </c>
       <c r="G320" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H320" t="str">
         <v>NONONO</v>
@@ -12582,7 +12582,7 @@
         <v/>
       </c>
       <c r="G321" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H321" t="str">
         <v>Ok</v>
@@ -12620,7 +12620,7 @@
         <v/>
       </c>
       <c r="G322" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H322" t="str">
         <v>Ok</v>
@@ -12658,7 +12658,7 @@
         <v/>
       </c>
       <c r="G323" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H323" t="str">
         <v>Ok</v>
@@ -12696,7 +12696,7 @@
         <v/>
       </c>
       <c r="G324" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H324" t="str">
         <v>Ok</v>
@@ -12734,7 +12734,7 @@
         <v/>
       </c>
       <c r="G325" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H325" t="str">
         <v>NONONO</v>
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="G326" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H326" t="str">
         <v>Ok</v>
@@ -12810,7 +12810,7 @@
         <v/>
       </c>
       <c r="G327" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H327" t="str">
         <v>Ok</v>
@@ -12848,7 +12848,7 @@
         <v/>
       </c>
       <c r="G328" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H328" t="str">
         <v>Ok</v>
@@ -12886,7 +12886,7 @@
         <v/>
       </c>
       <c r="G329" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H329" t="str">
         <v>Ok</v>
@@ -12924,7 +12924,7 @@
         <v/>
       </c>
       <c r="G330" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H330" t="str">
         <v>Ok</v>
@@ -12962,7 +12962,7 @@
         <v/>
       </c>
       <c r="G331" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H331" t="str">
         <v>Ok</v>
@@ -13000,7 +13000,7 @@
         <v/>
       </c>
       <c r="G332" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H332" t="str">
         <v>Ok</v>
@@ -13038,7 +13038,7 @@
         <v/>
       </c>
       <c r="G333" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H333" t="str">
         <v>Ok</v>
@@ -13076,7 +13076,7 @@
         <v/>
       </c>
       <c r="G334" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H334" t="str">
         <v>Ok</v>
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="G335" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H335" t="str">
         <v>Ok</v>
@@ -13152,7 +13152,7 @@
         <v/>
       </c>
       <c r="G336" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H336" t="str">
         <v>Ok</v>
@@ -13190,7 +13190,7 @@
         <v/>
       </c>
       <c r="G337" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H337" t="str">
         <v>Ok</v>
@@ -13228,7 +13228,7 @@
         <v/>
       </c>
       <c r="G338" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H338" t="str">
         <v>Ok</v>
@@ -13266,7 +13266,7 @@
         <v/>
       </c>
       <c r="G339" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H339" t="str">
         <v>Ok</v>
@@ -13304,7 +13304,7 @@
         <v/>
       </c>
       <c r="G340" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H340" t="str">
         <v>Ok</v>
@@ -13342,7 +13342,7 @@
         <v/>
       </c>
       <c r="G341" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H341" t="str">
         <v>Ok</v>
@@ -13380,7 +13380,7 @@
         <v/>
       </c>
       <c r="G342" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H342" t="str">
         <v>Ok</v>
@@ -13418,7 +13418,7 @@
         <v/>
       </c>
       <c r="G343" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H343" t="str">
         <v>Ok</v>
@@ -13456,7 +13456,7 @@
         <v/>
       </c>
       <c r="G344" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H344" t="str">
         <v>Ok</v>
@@ -13494,7 +13494,7 @@
         <v/>
       </c>
       <c r="G345" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H345" t="str">
         <v>Ok</v>
@@ -13532,7 +13532,7 @@
         <v/>
       </c>
       <c r="G346" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H346" t="str">
         <v>Ok</v>
@@ -13570,7 +13570,7 @@
         <v/>
       </c>
       <c r="G347" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H347" t="str">
         <v>Ok</v>
@@ -13608,7 +13608,7 @@
         <v/>
       </c>
       <c r="G348" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H348" t="str">
         <v>Ok</v>
@@ -13646,7 +13646,7 @@
         <v/>
       </c>
       <c r="G349" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H349" t="str">
         <v>NONONO</v>
@@ -13684,7 +13684,7 @@
         <v/>
       </c>
       <c r="G350" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H350" t="str">
         <v>Ok</v>
@@ -13722,7 +13722,7 @@
         <v/>
       </c>
       <c r="G351" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H351" t="str">
         <v>Ok</v>
@@ -13760,7 +13760,7 @@
         <v/>
       </c>
       <c r="G352" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H352" t="str">
         <v>Ok</v>
@@ -13798,7 +13798,7 @@
         <v/>
       </c>
       <c r="G353" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H353" t="str">
         <v>Ok</v>
@@ -13836,7 +13836,7 @@
         <v/>
       </c>
       <c r="G354" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H354" t="str">
         <v>Ok</v>
@@ -13874,7 +13874,7 @@
         <v/>
       </c>
       <c r="G355" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H355" t="str">
         <v>Ok</v>
@@ -13912,7 +13912,7 @@
         <v/>
       </c>
       <c r="G356" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H356" t="str">
         <v>Ok</v>
@@ -13950,7 +13950,7 @@
         <v/>
       </c>
       <c r="G357" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H357" t="str">
         <v>Ok</v>
@@ -13988,7 +13988,7 @@
         <v/>
       </c>
       <c r="G358" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H358" t="str">
         <v>Ok</v>
@@ -14026,7 +14026,7 @@
         <v/>
       </c>
       <c r="G359" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H359" t="str">
         <v>Ok</v>
@@ -14064,7 +14064,7 @@
         <v/>
       </c>
       <c r="G360" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H360" t="str">
         <v>Ok</v>
@@ -14102,7 +14102,7 @@
         <v/>
       </c>
       <c r="G361" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H361" t="str">
         <v>Ok</v>
@@ -14140,7 +14140,7 @@
         <v/>
       </c>
       <c r="G362" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H362" t="str">
         <v>Ok</v>
@@ -14178,7 +14178,7 @@
         <v/>
       </c>
       <c r="G363" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H363" t="str">
         <v>Ok</v>
@@ -14216,7 +14216,7 @@
         <v/>
       </c>
       <c r="G364" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H364" t="str">
         <v>NONONO</v>
@@ -14254,7 +14254,7 @@
         <v/>
       </c>
       <c r="G365" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H365" t="str">
         <v>NONONO</v>
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
       <c r="G366" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H366" t="str">
         <v>NONONO</v>
@@ -14330,7 +14330,7 @@
         <v/>
       </c>
       <c r="G367" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H367" t="str">
         <v>NONONO</v>
@@ -14368,7 +14368,7 @@
         <v/>
       </c>
       <c r="G368" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H368" t="str">
         <v>Ok</v>
@@ -14406,7 +14406,7 @@
         <v/>
       </c>
       <c r="G369" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H369" t="str">
         <v>NONONO</v>
@@ -14444,7 +14444,7 @@
         <v/>
       </c>
       <c r="G370" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H370" t="str">
         <v>Ok</v>
@@ -14482,7 +14482,7 @@
         <v/>
       </c>
       <c r="G371" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H371" t="str">
         <v>NONONO</v>
@@ -14520,7 +14520,7 @@
         <v/>
       </c>
       <c r="G372" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H372" t="str">
         <v>NONONO</v>
@@ -14558,7 +14558,7 @@
         <v/>
       </c>
       <c r="G373" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H373" t="str">
         <v>Ok</v>
@@ -14596,7 +14596,7 @@
         <v/>
       </c>
       <c r="G374" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H374" t="str">
         <v>Ok</v>
@@ -14634,7 +14634,7 @@
         <v/>
       </c>
       <c r="G375" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H375" t="str">
         <v>Ok</v>
@@ -14672,7 +14672,7 @@
         <v/>
       </c>
       <c r="G376" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H376" t="str">
         <v>Ok</v>
@@ -14710,7 +14710,7 @@
         <v/>
       </c>
       <c r="G377" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H377" t="str">
         <v>NONONO</v>
@@ -14748,7 +14748,7 @@
         <v/>
       </c>
       <c r="G378" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H378" t="str">
         <v>Ok</v>
@@ -14786,7 +14786,7 @@
         <v/>
       </c>
       <c r="G379" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H379" t="str">
         <v>NONONO</v>
@@ -14824,7 +14824,7 @@
         <v/>
       </c>
       <c r="G380" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H380" t="str">
         <v>Ok</v>
@@ -14862,7 +14862,7 @@
         <v/>
       </c>
       <c r="G381" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H381" t="str">
         <v>Ok</v>
@@ -14900,7 +14900,7 @@
         <v/>
       </c>
       <c r="G382" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H382" t="str">
         <v>Ok</v>
@@ -14938,7 +14938,7 @@
         <v/>
       </c>
       <c r="G383" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H383" t="str">
         <v>Ok</v>
@@ -14976,7 +14976,7 @@
         <v/>
       </c>
       <c r="G384" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H384" t="str">
         <v>Ok</v>
@@ -15014,7 +15014,7 @@
         <v/>
       </c>
       <c r="G385" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H385" t="str">
         <v>Ok</v>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
       <c r="G386" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H386" t="str">
         <v>Ok</v>
@@ -15090,7 +15090,7 @@
         <v/>
       </c>
       <c r="G387" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H387" t="str">
         <v>NONONO</v>
@@ -15128,7 +15128,7 @@
         <v/>
       </c>
       <c r="G388" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H388" t="str">
         <v>Ok</v>
@@ -15166,7 +15166,7 @@
         <v/>
       </c>
       <c r="G389" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H389" t="str">
         <v>Ok</v>
@@ -15204,7 +15204,7 @@
         <v/>
       </c>
       <c r="G390" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H390" t="str">
         <v>Ok</v>
@@ -15242,7 +15242,7 @@
         <v/>
       </c>
       <c r="G391" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H391" t="str">
         <v>Ok</v>
@@ -15280,7 +15280,7 @@
         <v/>
       </c>
       <c r="G392" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H392" t="str">
         <v>Ok</v>
@@ -15318,7 +15318,7 @@
         <v/>
       </c>
       <c r="G393" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H393" t="str">
         <v>NONONO</v>
@@ -15356,7 +15356,7 @@
         <v/>
       </c>
       <c r="G394" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H394" t="str">
         <v>Ok</v>
@@ -15394,7 +15394,7 @@
         <v/>
       </c>
       <c r="G395" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H395" t="str">
         <v>Ok</v>
@@ -15432,7 +15432,7 @@
         <v/>
       </c>
       <c r="G396" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H396" t="str">
         <v>Ok</v>
@@ -15470,7 +15470,7 @@
         <v/>
       </c>
       <c r="G397" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H397" t="str">
         <v>Ok</v>
@@ -15508,7 +15508,7 @@
         <v/>
       </c>
       <c r="G398" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H398" t="str">
         <v>Ok</v>
@@ -15546,7 +15546,7 @@
         <v/>
       </c>
       <c r="G399" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H399" t="str">
         <v>Ok</v>
@@ -15584,7 +15584,7 @@
         <v/>
       </c>
       <c r="G400" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H400" t="str">
         <v>Ok</v>
@@ -15622,7 +15622,7 @@
         <v/>
       </c>
       <c r="G401" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H401" t="str">
         <v>Ok</v>
@@ -15660,7 +15660,7 @@
         <v/>
       </c>
       <c r="G402" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H402" t="str">
         <v>Ok</v>
@@ -15698,7 +15698,7 @@
         <v/>
       </c>
       <c r="G403" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H403" t="str">
         <v>Ok</v>
@@ -15736,7 +15736,7 @@
         <v/>
       </c>
       <c r="G404" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H404" t="str">
         <v>Ok</v>
@@ -15774,7 +15774,7 @@
         <v/>
       </c>
       <c r="G405" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H405" t="str">
         <v>Ok</v>
@@ -15812,7 +15812,7 @@
         <v/>
       </c>
       <c r="G406" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H406" t="str">
         <v>Ok</v>
@@ -15850,7 +15850,7 @@
         <v/>
       </c>
       <c r="G407" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H407" t="str">
         <v>Ok</v>
@@ -15888,7 +15888,7 @@
         <v/>
       </c>
       <c r="G408" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H408" t="str">
         <v>Ok</v>
@@ -15926,7 +15926,7 @@
         <v/>
       </c>
       <c r="G409" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H409" t="str">
         <v>Ok</v>
@@ -15964,7 +15964,7 @@
         <v/>
       </c>
       <c r="G410" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H410" t="str">
         <v>Ok</v>
@@ -16002,7 +16002,7 @@
         <v/>
       </c>
       <c r="G411" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H411" t="str">
         <v>Ok</v>
@@ -16040,7 +16040,7 @@
         <v/>
       </c>
       <c r="G412" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H412" t="str">
         <v>Ok</v>
@@ -16078,7 +16078,7 @@
         <v/>
       </c>
       <c r="G413" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H413" t="str">
         <v>Ok</v>
@@ -16116,7 +16116,7 @@
         <v/>
       </c>
       <c r="G414" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H414" t="str">
         <v>Ok</v>
@@ -16154,7 +16154,7 @@
         <v/>
       </c>
       <c r="G415" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H415" t="str">
         <v>Ok</v>
@@ -16192,7 +16192,7 @@
         <v/>
       </c>
       <c r="G416" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H416" t="str">
         <v>NONONO</v>
@@ -16230,7 +16230,7 @@
         <v/>
       </c>
       <c r="G417" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H417" t="str">
         <v>NONONO</v>
@@ -16268,7 +16268,7 @@
         <v/>
       </c>
       <c r="G418" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H418" t="str">
         <v>Ok</v>
@@ -16306,7 +16306,7 @@
         <v/>
       </c>
       <c r="G419" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H419" t="str">
         <v>NONONO</v>
@@ -16344,7 +16344,7 @@
         <v/>
       </c>
       <c r="G420" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H420" t="str">
         <v>NONONO</v>
@@ -16382,7 +16382,7 @@
         <v/>
       </c>
       <c r="G421" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H421" t="str">
         <v>Ok</v>
@@ -16420,7 +16420,7 @@
         <v/>
       </c>
       <c r="G422" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H422" t="str">
         <v>NONONO</v>
@@ -16458,7 +16458,7 @@
         <v/>
       </c>
       <c r="G423" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H423" t="str">
         <v>Ok</v>
@@ -16496,7 +16496,7 @@
         <v/>
       </c>
       <c r="G424" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H424" t="str">
         <v>Ok</v>
@@ -16534,7 +16534,7 @@
         <v/>
       </c>
       <c r="G425" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H425" t="str">
         <v>Ok</v>
@@ -16572,7 +16572,7 @@
         <v/>
       </c>
       <c r="G426" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H426" t="str">
         <v>Ok</v>
@@ -16610,7 +16610,7 @@
         <v/>
       </c>
       <c r="G427" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H427" t="str">
         <v>Ok</v>
@@ -16648,7 +16648,7 @@
         <v/>
       </c>
       <c r="G428" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H428" t="str">
         <v>Ok</v>
@@ -16686,7 +16686,7 @@
         <v/>
       </c>
       <c r="G429" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H429" t="str">
         <v>Ok</v>
@@ -16724,7 +16724,7 @@
         <v/>
       </c>
       <c r="G430" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H430" t="str">
         <v>NONONO</v>
@@ -16762,7 +16762,7 @@
         <v/>
       </c>
       <c r="G431" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H431" t="str">
         <v>NONONO</v>
@@ -16800,7 +16800,7 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H432" t="str">
         <v>NONONO</v>
@@ -16838,7 +16838,7 @@
         <v/>
       </c>
       <c r="G433" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H433" t="str">
         <v>Ok</v>
@@ -16876,7 +16876,7 @@
         <v/>
       </c>
       <c r="G434" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H434" t="str">
         <v>Ok</v>
@@ -16914,7 +16914,7 @@
         <v/>
       </c>
       <c r="G435" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H435" t="str">
         <v>Ok</v>
@@ -16952,7 +16952,7 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H436" t="str">
         <v>Ok</v>
@@ -16990,7 +16990,7 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H437" t="str">
         <v>Ok</v>
@@ -17028,7 +17028,7 @@
         <v/>
       </c>
       <c r="G438" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H438" t="str">
         <v>NONONO</v>
@@ -17066,7 +17066,7 @@
         <v/>
       </c>
       <c r="G439" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H439" t="str">
         <v>NONONO</v>
@@ -17104,7 +17104,7 @@
         <v/>
       </c>
       <c r="G440" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H440" t="str">
         <v>NONONO</v>
@@ -17142,7 +17142,7 @@
         <v/>
       </c>
       <c r="G441" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H441" t="str">
         <v>NONONO</v>
@@ -17180,7 +17180,7 @@
         <v/>
       </c>
       <c r="G442" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H442" t="str">
         <v>NONONO</v>
@@ -17218,7 +17218,7 @@
         <v/>
       </c>
       <c r="G443" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H443" t="str">
         <v>NONONO</v>
@@ -17256,7 +17256,7 @@
         <v/>
       </c>
       <c r="G444" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H444" t="str">
         <v>NONONO</v>
@@ -17294,7 +17294,7 @@
         <v/>
       </c>
       <c r="G445" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H445" t="str">
         <v>NONONO</v>
@@ -17332,7 +17332,7 @@
         <v/>
       </c>
       <c r="G446" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H446" t="str">
         <v>NONONO</v>

--- a/8_Galar_Data.xlsx
+++ b/8_Galar_Data.xlsx
@@ -1879,7 +1879,7 @@
         <v>10-14</v>
       </c>
       <c r="G32" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H32" s="1">
         <v>0.15</v>
@@ -1926,7 +1926,7 @@
         <v>10-14</v>
       </c>
       <c r="G33" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H33" s="1">
         <v>0.15</v>
@@ -1973,7 +1973,7 @@
         <v>10-14</v>
       </c>
       <c r="G34" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H34" s="1">
         <v>0.15</v>
@@ -2020,7 +2020,7 @@
         <v>10-14</v>
       </c>
       <c r="G35" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H35" s="1">
         <v>0.15</v>
@@ -2067,7 +2067,7 @@
         <v>10-14</v>
       </c>
       <c r="G36" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H36" s="1">
         <v>0.1</v>
@@ -2114,7 +2114,7 @@
         <v>10-14</v>
       </c>
       <c r="G37" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H37" s="1">
         <v>0.1</v>
@@ -2161,7 +2161,7 @@
         <v>10-14</v>
       </c>
       <c r="G38" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H38" s="1">
         <v>0.1</v>
@@ -2208,7 +2208,7 @@
         <v>10-14</v>
       </c>
       <c r="G39" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H39" s="1">
         <v>0.05</v>
@@ -2255,7 +2255,7 @@
         <v>10-14</v>
       </c>
       <c r="G40" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H40" s="1">
         <v>0.05</v>
@@ -2302,7 +2302,7 @@
         <v>12-16</v>
       </c>
       <c r="G41" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H41" s="1">
         <v>0.15</v>
@@ -2349,7 +2349,7 @@
         <v>12-16</v>
       </c>
       <c r="G42" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H42" s="1">
         <v>0.15</v>
@@ -2396,7 +2396,7 @@
         <v>12-16</v>
       </c>
       <c r="G43" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H43" s="1">
         <v>0.15</v>
@@ -2443,7 +2443,7 @@
         <v>12-16</v>
       </c>
       <c r="G44" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H44" s="1">
         <v>0.15</v>
@@ -2490,7 +2490,7 @@
         <v>12-16</v>
       </c>
       <c r="G45" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H45" s="1">
         <v>0.1</v>
@@ -2537,7 +2537,7 @@
         <v>12-16</v>
       </c>
       <c r="G46" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H46" s="1">
         <v>0.1</v>
@@ -2584,7 +2584,7 @@
         <v>12-16</v>
       </c>
       <c r="G47" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H47" s="1">
         <v>0.1</v>
@@ -2631,7 +2631,7 @@
         <v>12-16</v>
       </c>
       <c r="G48" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H48" s="1">
         <v>0.05</v>
@@ -2678,7 +2678,7 @@
         <v>12-16</v>
       </c>
       <c r="G49" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H49" s="1">
         <v>0.05</v>
@@ -3007,7 +3007,7 @@
         <v>17-21</v>
       </c>
       <c r="G56" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H56" s="1">
         <v>0.15</v>
@@ -3054,7 +3054,7 @@
         <v>17-21</v>
       </c>
       <c r="G57" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H57" s="1">
         <v>0.15</v>
@@ -3101,7 +3101,7 @@
         <v>17-21</v>
       </c>
       <c r="G58" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H58" s="1">
         <v>0.15</v>
@@ -3148,7 +3148,7 @@
         <v>17-21</v>
       </c>
       <c r="G59" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H59" s="1">
         <v>0.15</v>
@@ -3195,7 +3195,7 @@
         <v>17-21</v>
       </c>
       <c r="G60" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H60" s="1">
         <v>0.1</v>
@@ -3242,7 +3242,7 @@
         <v>17-21</v>
       </c>
       <c r="G61" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H61" s="1">
         <v>0.1</v>
@@ -3289,7 +3289,7 @@
         <v>17-21</v>
       </c>
       <c r="G62" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H62" s="1">
         <v>0.1</v>
@@ -3336,7 +3336,7 @@
         <v>17-21</v>
       </c>
       <c r="G63" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H63" s="1">
         <v>0.1</v>
@@ -4229,7 +4229,7 @@
         <v>24-28</v>
       </c>
       <c r="G82" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H82" s="1">
         <v>0.1</v>
@@ -4276,7 +4276,7 @@
         <v>24-28</v>
       </c>
       <c r="G83" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H83" s="1">
         <v>0.1</v>
@@ -4323,7 +4323,7 @@
         <v>24-28</v>
       </c>
       <c r="G84" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H84" s="1">
         <v>0.1</v>
@@ -4370,7 +4370,7 @@
         <v>24-28</v>
       </c>
       <c r="G85" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H85" s="1">
         <v>0.1</v>
@@ -4417,7 +4417,7 @@
         <v>24-28</v>
       </c>
       <c r="G86" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H86" s="1">
         <v>0.1</v>
@@ -4464,7 +4464,7 @@
         <v>24-28</v>
       </c>
       <c r="G87" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H87" s="1">
         <v>0.1</v>
@@ -4511,7 +4511,7 @@
         <v>24-28</v>
       </c>
       <c r="G88" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H88" s="1">
         <v>0.1</v>
@@ -4558,7 +4558,7 @@
         <v>24-28</v>
       </c>
       <c r="G89" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H89" s="1">
         <v>0.1</v>
@@ -4605,7 +4605,7 @@
         <v>24-28</v>
       </c>
       <c r="G90" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H90" s="1">
         <v>0.1</v>
@@ -4652,7 +4652,7 @@
         <v>24-28</v>
       </c>
       <c r="G91" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H91" s="1">
         <v>0.1</v>
@@ -5122,7 +5122,7 @@
         <v>28-32</v>
       </c>
       <c r="G101" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H101" s="1">
         <v>0.15</v>
@@ -5169,7 +5169,7 @@
         <v>28-32</v>
       </c>
       <c r="G102" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H102" s="1">
         <v>0.15</v>
@@ -5216,7 +5216,7 @@
         <v>28-32</v>
       </c>
       <c r="G103" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H103" s="1">
         <v>0.15</v>
@@ -5263,7 +5263,7 @@
         <v>28-32</v>
       </c>
       <c r="G104" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H104" s="1">
         <v>0.15</v>
@@ -5310,7 +5310,7 @@
         <v>28-32</v>
       </c>
       <c r="G105" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H105" s="1">
         <v>0.1</v>
@@ -5357,7 +5357,7 @@
         <v>28-32</v>
       </c>
       <c r="G106" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H106" s="1">
         <v>0.1</v>
@@ -5404,7 +5404,7 @@
         <v>28-32</v>
       </c>
       <c r="G107" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H107" s="1">
         <v>0.1</v>
@@ -5451,7 +5451,7 @@
         <v>28-32</v>
       </c>
       <c r="G108" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H108" s="1">
         <v>0.05</v>
@@ -5498,7 +5498,7 @@
         <v>28-32</v>
       </c>
       <c r="G109" t="str">
-        <v>17-20</v>
+        <v>16-19</v>
       </c>
       <c r="H109" s="1">
         <v>0.05</v>
@@ -6109,7 +6109,7 @@
         <v>35-39</v>
       </c>
       <c r="G122" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H122" s="1">
         <v>0.15</v>
@@ -6156,7 +6156,7 @@
         <v>35-39</v>
       </c>
       <c r="G123" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H123" s="1">
         <v>0.15</v>
@@ -6203,7 +6203,7 @@
         <v>35-39</v>
       </c>
       <c r="G124" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H124" s="1">
         <v>0.15</v>
@@ -6250,7 +6250,7 @@
         <v>35-39</v>
       </c>
       <c r="G125" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H125" s="1">
         <v>0.15</v>
@@ -6297,7 +6297,7 @@
         <v>35-39</v>
       </c>
       <c r="G126" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H126" s="1">
         <v>0.1</v>
@@ -6344,7 +6344,7 @@
         <v>35-39</v>
       </c>
       <c r="G127" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H127" s="1">
         <v>0.1</v>
@@ -6391,7 +6391,7 @@
         <v>35-39</v>
       </c>
       <c r="G128" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H128" s="1">
         <v>0.1</v>
@@ -6438,7 +6438,7 @@
         <v>35-39</v>
       </c>
       <c r="G129" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H129" s="1">
         <v>0.1</v>
@@ -6861,7 +6861,7 @@
         <v>40-44</v>
       </c>
       <c r="G138" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H138" s="1">
         <v>0.2</v>
@@ -6908,7 +6908,7 @@
         <v>40-44</v>
       </c>
       <c r="G139" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H139" s="1">
         <v>0.15</v>
@@ -6955,7 +6955,7 @@
         <v>40-44</v>
       </c>
       <c r="G140" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H140" s="1">
         <v>0.15</v>
@@ -7002,7 +7002,7 @@
         <v>40-44</v>
       </c>
       <c r="G141" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H141" s="1">
         <v>0.15</v>
@@ -7049,7 +7049,7 @@
         <v>40-44</v>
       </c>
       <c r="G142" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H142" s="1">
         <v>0.15</v>
@@ -7096,7 +7096,7 @@
         <v>40-44</v>
       </c>
       <c r="G143" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H143" s="1">
         <v>0.1</v>
@@ -7143,7 +7143,7 @@
         <v>40-44</v>
       </c>
       <c r="G144" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H144" s="1">
         <v>0.1</v>
@@ -8600,7 +8600,7 @@
         <v>47-51</v>
       </c>
       <c r="G175" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H175" s="1">
         <v>0.19</v>
@@ -8647,7 +8647,7 @@
         <v>47-51</v>
       </c>
       <c r="G176" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H176" s="1">
         <v>0.19</v>
@@ -8694,7 +8694,7 @@
         <v>47-51</v>
       </c>
       <c r="G177" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H177" s="1">
         <v>0.19</v>
@@ -8741,7 +8741,7 @@
         <v>47-51</v>
       </c>
       <c r="G178" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H178" s="1">
         <v>0.14</v>
@@ -8788,7 +8788,7 @@
         <v>47-51</v>
       </c>
       <c r="G179" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H179" s="1">
         <v>0.14</v>
@@ -8835,7 +8835,7 @@
         <v>47-51</v>
       </c>
       <c r="G180" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H180" s="1">
         <v>0.1</v>
@@ -8882,7 +8882,7 @@
         <v>47-51</v>
       </c>
       <c r="G181" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H181" s="1">
         <v>0.05</v>
@@ -8929,7 +8929,7 @@
         <v>49-53</v>
       </c>
       <c r="G182" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H182" s="1">
         <v>0.15</v>
@@ -8976,7 +8976,7 @@
         <v>49-53</v>
       </c>
       <c r="G183" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H183" s="1">
         <v>0.15</v>
@@ -9023,7 +9023,7 @@
         <v>49-53</v>
       </c>
       <c r="G184" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H184" s="1">
         <v>0.15</v>
@@ -9070,7 +9070,7 @@
         <v>49-53</v>
       </c>
       <c r="G185" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H185" s="1">
         <v>0.15</v>
@@ -9117,7 +9117,7 @@
         <v>49-53</v>
       </c>
       <c r="G186" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H186" s="1">
         <v>0.1</v>
@@ -9164,7 +9164,7 @@
         <v>49-53</v>
       </c>
       <c r="G187" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H187" s="1">
         <v>0.1</v>
@@ -9211,7 +9211,7 @@
         <v>49-53</v>
       </c>
       <c r="G188" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H188" s="1">
         <v>0.1</v>
@@ -9258,7 +9258,7 @@
         <v>49-53</v>
       </c>
       <c r="G189" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
@@ -9305,7 +9305,7 @@
         <v>51-55</v>
       </c>
       <c r="G190" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H190" s="1">
         <v>0.2</v>
@@ -9352,7 +9352,7 @@
         <v>51-55</v>
       </c>
       <c r="G191" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H191" s="1">
         <v>0.2</v>
@@ -9399,7 +9399,7 @@
         <v>51-55</v>
       </c>
       <c r="G192" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H192" s="1">
         <v>0.2</v>
@@ -9446,7 +9446,7 @@
         <v>51-55</v>
       </c>
       <c r="G193" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H193" s="1">
         <v>0.15</v>
@@ -9493,7 +9493,7 @@
         <v>51-55</v>
       </c>
       <c r="G194" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H194" s="1">
         <v>0.15</v>
@@ -9540,7 +9540,7 @@
         <v>51-55</v>
       </c>
       <c r="G195" t="str">
-        <v>33-37</v>
+        <v>32-35</v>
       </c>
       <c r="H195" s="1">
         <v>0.1</v>
@@ -9587,7 +9587,7 @@
         <v>53-58</v>
       </c>
       <c r="G196" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H196" s="1">
         <v>0.15</v>
@@ -9634,7 +9634,7 @@
         <v>53-58</v>
       </c>
       <c r="G197" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H197" s="1">
         <v>0.15</v>
@@ -9681,7 +9681,7 @@
         <v>53-58</v>
       </c>
       <c r="G198" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H198" s="1">
         <v>0.15</v>
@@ -9728,7 +9728,7 @@
         <v>53-58</v>
       </c>
       <c r="G199" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H199" s="1">
         <v>0.15</v>
@@ -9775,7 +9775,7 @@
         <v>53-58</v>
       </c>
       <c r="G200" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H200" s="1">
         <v>0.1</v>
@@ -9822,7 +9822,7 @@
         <v>53-58</v>
       </c>
       <c r="G201" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H201" s="1">
         <v>0.1</v>
@@ -9869,7 +9869,7 @@
         <v>53-58</v>
       </c>
       <c r="G202" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H202" s="1">
         <v>0.1</v>
@@ -9916,7 +9916,7 @@
         <v>53-58</v>
       </c>
       <c r="G203" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H203" s="1">
         <v>0.05</v>
@@ -9963,7 +9963,7 @@
         <v>53-58</v>
       </c>
       <c r="G204" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H204" s="1">
         <v>0.05</v>
@@ -10010,7 +10010,7 @@
         <v>56-60</v>
       </c>
       <c r="G205" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H205" s="1">
         <v>0.15</v>
@@ -10057,7 +10057,7 @@
         <v>56-60</v>
       </c>
       <c r="G206" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H206" s="1">
         <v>0.15</v>
@@ -10104,7 +10104,7 @@
         <v>56-60</v>
       </c>
       <c r="G207" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H207" s="1">
         <v>0.15</v>
@@ -10151,7 +10151,7 @@
         <v>56-60</v>
       </c>
       <c r="G208" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H208" s="1">
         <v>0.15</v>
@@ -10198,7 +10198,7 @@
         <v>56-60</v>
       </c>
       <c r="G209" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H209" s="1">
         <v>0.1</v>
@@ -10245,7 +10245,7 @@
         <v>56-60</v>
       </c>
       <c r="G210" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H210" s="1">
         <v>0.1</v>
@@ -10292,7 +10292,7 @@
         <v>56-60</v>
       </c>
       <c r="G211" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H211" s="1">
         <v>0.1</v>
@@ -10339,7 +10339,7 @@
         <v>56-60</v>
       </c>
       <c r="G212" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H212" s="1">
         <v>0.05</v>
@@ -10386,7 +10386,7 @@
         <v>56-60</v>
       </c>
       <c r="G213" t="str">
-        <v>36-40</v>
+        <v>36-39</v>
       </c>
       <c r="H213" s="1">
         <v>0.05</v>
@@ -10433,7 +10433,7 @@
         <v>58-62</v>
       </c>
       <c r="G214" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H214" s="1">
         <v>0.09</v>
@@ -10480,7 +10480,7 @@
         <v>58-62</v>
       </c>
       <c r="G215" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H215" s="1">
         <v>0.09</v>
@@ -10527,7 +10527,7 @@
         <v>58-62</v>
       </c>
       <c r="G216" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H216" s="1">
         <v>0.09</v>
@@ -10574,7 +10574,7 @@
         <v>58-62</v>
       </c>
       <c r="G217" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H217" s="1">
         <v>0.09</v>
@@ -10621,7 +10621,7 @@
         <v>58-62</v>
       </c>
       <c r="G218" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H218" s="1">
         <v>0.09</v>
@@ -10668,7 +10668,7 @@
         <v>58-62</v>
       </c>
       <c r="G219" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H219" s="1">
         <v>0.09</v>
@@ -10715,7 +10715,7 @@
         <v>58-62</v>
       </c>
       <c r="G220" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H220" s="1">
         <v>0.09</v>
@@ -10762,7 +10762,7 @@
         <v>58-62</v>
       </c>
       <c r="G221" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H221" s="1">
         <v>0.09</v>
@@ -10809,7 +10809,7 @@
         <v>58-62</v>
       </c>
       <c r="G222" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H222" s="1">
         <v>0.09</v>
@@ -10856,7 +10856,7 @@
         <v>58-62</v>
       </c>
       <c r="G223" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H223" s="1">
         <v>0.09</v>
@@ -10903,7 +10903,7 @@
         <v>58-62</v>
       </c>
       <c r="G224" t="str">
-        <v>38-42</v>
+        <v>37-40</v>
       </c>
       <c r="H224" s="1">
         <v>0.09</v>
@@ -10950,7 +10950,7 @@
         <v>60-65</v>
       </c>
       <c r="G225" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H225" s="1">
         <v>0.07</v>
@@ -10997,7 +10997,7 @@
         <v>60-65</v>
       </c>
       <c r="G226" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H226" s="1">
         <v>0.07</v>
@@ -11044,7 +11044,7 @@
         <v>60-65</v>
       </c>
       <c r="G227" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H227" s="1">
         <v>0.07</v>
@@ -11091,7 +11091,7 @@
         <v>60-65</v>
       </c>
       <c r="G228" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H228" s="1">
         <v>0.07</v>
@@ -11138,7 +11138,7 @@
         <v>60-65</v>
       </c>
       <c r="G229" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H229" s="1">
         <v>0.07</v>
@@ -11185,7 +11185,7 @@
         <v>60-65</v>
       </c>
       <c r="G230" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H230" s="1">
         <v>0.07</v>
@@ -11232,7 +11232,7 @@
         <v>60-65</v>
       </c>
       <c r="G231" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H231" s="1">
         <v>0.07</v>
@@ -11279,7 +11279,7 @@
         <v>60-65</v>
       </c>
       <c r="G232" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H232" s="1">
         <v>0.07</v>
@@ -11326,7 +11326,7 @@
         <v>60-65</v>
       </c>
       <c r="G233" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H233" s="1">
         <v>0.07</v>
@@ -11373,7 +11373,7 @@
         <v>60-65</v>
       </c>
       <c r="G234" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H234" s="1">
         <v>0.07</v>
@@ -11420,7 +11420,7 @@
         <v>60-65</v>
       </c>
       <c r="G235" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H235" s="1">
         <v>0.07</v>
@@ -11467,7 +11467,7 @@
         <v>60-65</v>
       </c>
       <c r="G236" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H236" s="1">
         <v>0.07</v>
@@ -11514,7 +11514,7 @@
         <v>60-65</v>
       </c>
       <c r="G237" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H237" s="1">
         <v>0.07</v>
@@ -11561,7 +11561,7 @@
         <v>60-65</v>
       </c>
       <c r="G238" t="str">
-        <v>39-43</v>
+        <v>39-42</v>
       </c>
       <c r="H238" s="1">
         <v>0.07</v>
@@ -11608,7 +11608,7 @@
         <v>63-67</v>
       </c>
       <c r="G239" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H239" s="1">
         <v>0.15</v>
@@ -11655,7 +11655,7 @@
         <v>63-67</v>
       </c>
       <c r="G240" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H240" s="1">
         <v>0.15</v>
@@ -11702,7 +11702,7 @@
         <v>63-67</v>
       </c>
       <c r="G241" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H241" s="1">
         <v>0.15</v>
@@ -11749,7 +11749,7 @@
         <v>63-67</v>
       </c>
       <c r="G242" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H242" s="1">
         <v>0.15</v>
@@ -11796,7 +11796,7 @@
         <v>63-67</v>
       </c>
       <c r="G243" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H243" s="1">
         <v>0.1</v>
@@ -11843,7 +11843,7 @@
         <v>63-67</v>
       </c>
       <c r="G244" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H244" s="1">
         <v>0.1</v>
@@ -11890,7 +11890,7 @@
         <v>63-67</v>
       </c>
       <c r="G245" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H245" s="1">
         <v>0.1</v>
@@ -11937,7 +11937,7 @@
         <v>63-67</v>
       </c>
       <c r="G246" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H246" s="1">
         <v>0.05</v>
@@ -11984,7 +11984,7 @@
         <v>63-67</v>
       </c>
       <c r="G247" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H247" s="1">
         <v>0.05</v>
@@ -12031,7 +12031,7 @@
         <v>65-69</v>
       </c>
       <c r="G248" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H248" s="1">
         <v>0.15</v>
@@ -12078,7 +12078,7 @@
         <v>65-69</v>
       </c>
       <c r="G249" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H249" s="1">
         <v>0.15</v>
@@ -12125,7 +12125,7 @@
         <v>65-69</v>
       </c>
       <c r="G250" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H250" s="1">
         <v>0.15</v>
@@ -12172,7 +12172,7 @@
         <v>65-69</v>
       </c>
       <c r="G251" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H251" s="1">
         <v>0.15</v>
@@ -12219,7 +12219,7 @@
         <v>65-69</v>
       </c>
       <c r="G252" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H252" s="1">
         <v>0.1</v>
@@ -12266,7 +12266,7 @@
         <v>65-69</v>
       </c>
       <c r="G253" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H253" s="1">
         <v>0.1</v>
@@ -12313,7 +12313,7 @@
         <v>65-69</v>
       </c>
       <c r="G254" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H254" s="1">
         <v>0.1</v>
@@ -12360,7 +12360,7 @@
         <v>65-69</v>
       </c>
       <c r="G255" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H255" s="1">
         <v>0.05</v>
@@ -12407,7 +12407,7 @@
         <v>65-69</v>
       </c>
       <c r="G256" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H256" s="1">
         <v>0.05</v>
@@ -12454,7 +12454,7 @@
         <v>65-69</v>
       </c>
       <c r="G257" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H257" s="1">
         <v>0.05</v>
@@ -12501,7 +12501,7 @@
         <v>67-70</v>
       </c>
       <c r="G258" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H258" s="1">
         <v>0.15</v>
@@ -12548,7 +12548,7 @@
         <v>67-70</v>
       </c>
       <c r="G259" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H259" s="1">
         <v>0.15</v>
@@ -12595,7 +12595,7 @@
         <v>67-70</v>
       </c>
       <c r="G260" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H260" s="1">
         <v>0.15</v>
@@ -12642,7 +12642,7 @@
         <v>67-70</v>
       </c>
       <c r="G261" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H261" s="1">
         <v>0.15</v>
@@ -12689,7 +12689,7 @@
         <v>67-70</v>
       </c>
       <c r="G262" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H262" s="1">
         <v>0.1</v>
@@ -12736,7 +12736,7 @@
         <v>67-70</v>
       </c>
       <c r="G263" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H263" s="1">
         <v>0.1</v>
@@ -12783,7 +12783,7 @@
         <v>67-70</v>
       </c>
       <c r="G264" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H264" s="1">
         <v>0.1</v>
@@ -12830,7 +12830,7 @@
         <v>67-70</v>
       </c>
       <c r="G265" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H265" s="1">
         <v>0.05</v>
@@ -12877,7 +12877,7 @@
         <v>67-70</v>
       </c>
       <c r="G266" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H266" s="1">
         <v>0.05</v>
@@ -12924,7 +12924,7 @@
         <v>67-70</v>
       </c>
       <c r="G267" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H267" s="1">
         <v>0.05</v>
@@ -12971,7 +12971,7 @@
         <v>70-70</v>
       </c>
       <c r="G268" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H268" s="1">
         <v>0.14</v>
@@ -13018,7 +13018,7 @@
         <v>70-70</v>
       </c>
       <c r="G269" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H269" s="1">
         <v>0.14</v>
@@ -13065,7 +13065,7 @@
         <v>70-70</v>
       </c>
       <c r="G270" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H270" s="1">
         <v>0.14</v>
@@ -13112,7 +13112,7 @@
         <v>70-70</v>
       </c>
       <c r="G271" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H271" s="1">
         <v>0.14</v>
@@ -13159,7 +13159,7 @@
         <v>70-70</v>
       </c>
       <c r="G272" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H272" s="1">
         <v>0.1</v>
@@ -13206,7 +13206,7 @@
         <v>70-70</v>
       </c>
       <c r="G273" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H273" s="1">
         <v>0.1</v>
@@ -13253,7 +13253,7 @@
         <v>70-70</v>
       </c>
       <c r="G274" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H274" s="1">
         <v>0.1</v>
@@ -13300,7 +13300,7 @@
         <v>70-70</v>
       </c>
       <c r="G275" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H275" s="1">
         <v>0.05</v>
@@ -13347,7 +13347,7 @@
         <v>70-70</v>
       </c>
       <c r="G276" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H276" s="1">
         <v>0.05</v>
@@ -13394,7 +13394,7 @@
         <v>70-70</v>
       </c>
       <c r="G277" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H277" s="1">
         <v>0.05</v>
@@ -13441,7 +13441,7 @@
         <v>15-20</v>
       </c>
       <c r="G278" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H278" s="1">
         <v>0.2</v>
@@ -13488,7 +13488,7 @@
         <v>15-20</v>
       </c>
       <c r="G279" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H279" s="1">
         <v>0.15</v>
@@ -13535,7 +13535,7 @@
         <v>15-20</v>
       </c>
       <c r="G280" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H280" s="1">
         <v>0.15</v>
@@ -13582,7 +13582,7 @@
         <v>15-20</v>
       </c>
       <c r="G281" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H281" s="1">
         <v>0.15</v>
@@ -13629,7 +13629,7 @@
         <v>15-20</v>
       </c>
       <c r="G282" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H282" s="1">
         <v>0.15</v>
@@ -13676,7 +13676,7 @@
         <v>15-20</v>
       </c>
       <c r="G283" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H283" s="1">
         <v>0.1</v>
@@ -13723,7 +13723,7 @@
         <v>15-20</v>
       </c>
       <c r="G284" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H284" s="1">
         <v>0.1</v>
@@ -13770,7 +13770,7 @@
         <v>18-24</v>
       </c>
       <c r="G285" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H285" s="1">
         <v>0.15</v>
@@ -13817,7 +13817,7 @@
         <v>18-24</v>
       </c>
       <c r="G286" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H286" s="1">
         <v>0.15</v>
@@ -13864,7 +13864,7 @@
         <v>18-24</v>
       </c>
       <c r="G287" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H287" s="1">
         <v>0.15</v>
@@ -13911,7 +13911,7 @@
         <v>18-24</v>
       </c>
       <c r="G288" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H288" s="1">
         <v>0.15</v>
@@ -13958,7 +13958,7 @@
         <v>18-24</v>
       </c>
       <c r="G289" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H289" s="1">
         <v>0.1</v>
@@ -14005,7 +14005,7 @@
         <v>18-24</v>
       </c>
       <c r="G290" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H290" s="1">
         <v>0.1</v>
@@ -14052,7 +14052,7 @@
         <v>18-24</v>
       </c>
       <c r="G291" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H291" s="1">
         <v>0.1</v>
@@ -14099,7 +14099,7 @@
         <v>18-24</v>
       </c>
       <c r="G292" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H292" s="1">
         <v>0.05</v>
@@ -14146,7 +14146,7 @@
         <v>18-24</v>
       </c>
       <c r="G293" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H293" s="1">
         <v>0.05</v>
@@ -14193,7 +14193,7 @@
         <v>22-28</v>
       </c>
       <c r="G294" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H294" s="1">
         <v>0.15</v>
@@ -14240,7 +14240,7 @@
         <v>22-28</v>
       </c>
       <c r="G295" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H295" s="1">
         <v>0.15</v>
@@ -14287,7 +14287,7 @@
         <v>22-28</v>
       </c>
       <c r="G296" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H296" s="1">
         <v>0.15</v>
@@ -14334,7 +14334,7 @@
         <v>22-28</v>
       </c>
       <c r="G297" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H297" s="1">
         <v>0.15</v>
@@ -14381,7 +14381,7 @@
         <v>22-28</v>
       </c>
       <c r="G298" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H298" s="1">
         <v>0.1</v>
@@ -14428,7 +14428,7 @@
         <v>22-28</v>
       </c>
       <c r="G299" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H299" s="1">
         <v>0.1</v>
@@ -14475,7 +14475,7 @@
         <v>22-28</v>
       </c>
       <c r="G300" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H300" s="1">
         <v>0.1</v>
@@ -14522,7 +14522,7 @@
         <v>22-28</v>
       </c>
       <c r="G301" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H301" s="1">
         <v>0.05</v>
@@ -14569,7 +14569,7 @@
         <v>22-28</v>
       </c>
       <c r="G302" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H302" s="1">
         <v>0.05</v>
@@ -14616,7 +14616,7 @@
         <v>22-28</v>
       </c>
       <c r="G303" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H303" s="1">
         <v>0.05</v>
@@ -14663,7 +14663,7 @@
         <v>26-30</v>
       </c>
       <c r="G304" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H304" s="1">
         <v>0.15</v>
@@ -14710,7 +14710,7 @@
         <v>26-30</v>
       </c>
       <c r="G305" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H305" s="1">
         <v>0.15</v>
@@ -14757,7 +14757,7 @@
         <v>26-30</v>
       </c>
       <c r="G306" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H306" s="1">
         <v>0.15</v>
@@ -14804,7 +14804,7 @@
         <v>26-30</v>
       </c>
       <c r="G307" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H307" s="1">
         <v>0.15</v>
@@ -14851,7 +14851,7 @@
         <v>26-30</v>
       </c>
       <c r="G308" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H308" s="1">
         <v>0.1</v>
@@ -14898,7 +14898,7 @@
         <v>26-30</v>
       </c>
       <c r="G309" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H309" s="1">
         <v>0.1</v>
@@ -14945,7 +14945,7 @@
         <v>26-30</v>
       </c>
       <c r="G310" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H310" s="1">
         <v>0.1</v>
@@ -14992,7 +14992,7 @@
         <v>26-30</v>
       </c>
       <c r="G311" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H311" s="1">
         <v>0.05</v>
@@ -15039,7 +15039,7 @@
         <v>26-30</v>
       </c>
       <c r="G312" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H312" s="1">
         <v>0.05</v>
@@ -15086,7 +15086,7 @@
         <v>30-30</v>
       </c>
       <c r="G313" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H313" s="1">
         <v>1</v>
@@ -15133,7 +15133,7 @@
         <v>40-47</v>
       </c>
       <c r="G314" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H314" s="1">
         <v>0.2</v>
@@ -15180,7 +15180,7 @@
         <v>40-47</v>
       </c>
       <c r="G315" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H315" s="1">
         <v>0.2</v>
@@ -15227,7 +15227,7 @@
         <v>40-47</v>
       </c>
       <c r="G316" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H316" s="1">
         <v>0.2</v>
@@ -15274,7 +15274,7 @@
         <v>40-47</v>
       </c>
       <c r="G317" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H317" s="1">
         <v>0.15</v>
@@ -15321,7 +15321,7 @@
         <v>40-47</v>
       </c>
       <c r="G318" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H318" s="1">
         <v>0.15</v>
@@ -15368,7 +15368,7 @@
         <v>40-47</v>
       </c>
       <c r="G319" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H319" s="1">
         <v>0.1</v>
@@ -15415,7 +15415,7 @@
         <v>45-52</v>
       </c>
       <c r="G320" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H320" s="1">
         <v>0.15</v>
@@ -15462,7 +15462,7 @@
         <v>45-52</v>
       </c>
       <c r="G321" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H321" s="1">
         <v>0.15</v>
@@ -15509,7 +15509,7 @@
         <v>45-52</v>
       </c>
       <c r="G322" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H322" s="1">
         <v>0.15</v>
@@ -15556,7 +15556,7 @@
         <v>45-52</v>
       </c>
       <c r="G323" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H323" s="1">
         <v>0.15</v>
@@ -15603,7 +15603,7 @@
         <v>45-52</v>
       </c>
       <c r="G324" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H324" s="1">
         <v>0.1</v>
@@ -15650,7 +15650,7 @@
         <v>45-52</v>
       </c>
       <c r="G325" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H325" s="1">
         <v>0.1</v>
@@ -15697,7 +15697,7 @@
         <v>45-52</v>
       </c>
       <c r="G326" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H326" s="1">
         <v>0.1</v>
@@ -15744,7 +15744,7 @@
         <v>45-52</v>
       </c>
       <c r="G327" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H327" s="1">
         <v>0.05</v>
@@ -15791,7 +15791,7 @@
         <v>45-52</v>
       </c>
       <c r="G328" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H328" s="1">
         <v>0.05</v>
@@ -15838,7 +15838,7 @@
         <v>50-55</v>
       </c>
       <c r="G329" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H329" s="1">
         <v>0.15</v>
@@ -15885,7 +15885,7 @@
         <v>50-55</v>
       </c>
       <c r="G330" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H330" s="1">
         <v>0.15</v>
@@ -15932,7 +15932,7 @@
         <v>50-55</v>
       </c>
       <c r="G331" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H331" s="1">
         <v>0.15</v>
@@ -15979,7 +15979,7 @@
         <v>50-55</v>
       </c>
       <c r="G332" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H332" s="1">
         <v>0.15</v>
@@ -16026,7 +16026,7 @@
         <v>50-55</v>
       </c>
       <c r="G333" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H333" s="1">
         <v>0.1</v>
@@ -16073,7 +16073,7 @@
         <v>50-55</v>
       </c>
       <c r="G334" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H334" s="1">
         <v>0.1</v>
@@ -16120,7 +16120,7 @@
         <v>50-55</v>
       </c>
       <c r="G335" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H335" s="1">
         <v>0.1</v>
@@ -16167,7 +16167,7 @@
         <v>50-55</v>
       </c>
       <c r="G336" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H336" s="1">
         <v>0.1</v>
@@ -16214,7 +16214,7 @@
         <v>55-55</v>
       </c>
       <c r="G337" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H337" s="1">
         <v>0.25</v>
@@ -16261,7 +16261,7 @@
         <v>55-55</v>
       </c>
       <c r="G338" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H338" s="1">
         <v>0.25</v>
@@ -16308,7 +16308,7 @@
         <v>55-55</v>
       </c>
       <c r="G339" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H339" s="1">
         <v>0.2</v>
@@ -16355,7 +16355,7 @@
         <v>55-55</v>
       </c>
       <c r="G340" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H340" s="1">
         <v>0.15</v>
@@ -16402,7 +16402,7 @@
         <v>55-55</v>
       </c>
       <c r="G341" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H341" s="1">
         <v>0.15</v>
@@ -16449,7 +16449,7 @@
         <v>70-80</v>
       </c>
       <c r="G342" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H342" s="1">
         <v>0.15</v>
@@ -16496,7 +16496,7 @@
         <v>70-80</v>
       </c>
       <c r="G343" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H343" s="1">
         <v>0.15</v>
@@ -16543,7 +16543,7 @@
         <v>70-80</v>
       </c>
       <c r="G344" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H344" s="1">
         <v>0.15</v>
@@ -16590,7 +16590,7 @@
         <v>70-80</v>
       </c>
       <c r="G345" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H345" s="1">
         <v>0.15</v>
@@ -16637,7 +16637,7 @@
         <v>70-80</v>
       </c>
       <c r="G346" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H346" s="1">
         <v>0.1</v>
@@ -16684,7 +16684,7 @@
         <v>70-80</v>
       </c>
       <c r="G347" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H347" s="1">
         <v>0.1</v>
@@ -16731,7 +16731,7 @@
         <v>70-80</v>
       </c>
       <c r="G348" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H348" s="1">
         <v>0.1</v>
@@ -16778,7 +16778,7 @@
         <v>70-80</v>
       </c>
       <c r="G349" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H349" s="1">
         <v>0.05</v>
@@ -16825,7 +16825,7 @@
         <v>70-80</v>
       </c>
       <c r="G350" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H350" s="1">
         <v>0.05</v>
@@ -16872,7 +16872,7 @@
         <v>86-95</v>
       </c>
       <c r="G351" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H351" s="1">
         <v>0.3</v>
@@ -16919,7 +16919,7 @@
         <v>86-95</v>
       </c>
       <c r="G352" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H352" s="1">
         <v>0.25</v>
@@ -16966,7 +16966,7 @@
         <v>86-95</v>
       </c>
       <c r="G353" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H353" s="1">
         <v>0.25</v>
@@ -17013,7 +17013,7 @@
         <v>86-95</v>
       </c>
       <c r="G354" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H354" s="1">
         <v>0.2</v>
@@ -17060,7 +17060,7 @@
         <v>78-88</v>
       </c>
       <c r="G355" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H355" s="1">
         <v>0.15</v>
@@ -17107,7 +17107,7 @@
         <v>78-88</v>
       </c>
       <c r="G356" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H356" s="1">
         <v>0.15</v>
@@ -17154,7 +17154,7 @@
         <v>78-88</v>
       </c>
       <c r="G357" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H357" s="1">
         <v>0.15</v>
@@ -17201,7 +17201,7 @@
         <v>78-88</v>
       </c>
       <c r="G358" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H358" s="1">
         <v>0.15</v>
@@ -17248,7 +17248,7 @@
         <v>78-88</v>
       </c>
       <c r="G359" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H359" s="1">
         <v>0.1</v>
@@ -17295,7 +17295,7 @@
         <v>78-88</v>
       </c>
       <c r="G360" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H360" s="1">
         <v>0.1</v>
@@ -17342,7 +17342,7 @@
         <v>78-88</v>
       </c>
       <c r="G361" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H361" s="1">
         <v>0.1</v>
@@ -17389,7 +17389,7 @@
         <v>78-88</v>
       </c>
       <c r="G362" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H362" s="1">
         <v>0.05</v>
@@ -17436,7 +17436,7 @@
         <v>78-88</v>
       </c>
       <c r="G363" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H363" s="1">
         <v>0.05</v>
@@ -17483,7 +17483,7 @@
         <v>84-89</v>
       </c>
       <c r="G364" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H364" s="1">
         <v>1</v>
@@ -17530,7 +17530,7 @@
         <v>87-93</v>
       </c>
       <c r="G365" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H365" s="1">
         <v>1</v>
@@ -17577,7 +17577,7 @@
         <v>91-95</v>
       </c>
       <c r="G366" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H366" s="1">
         <v>1</v>
@@ -17624,7 +17624,7 @@
         <v>70-84</v>
       </c>
       <c r="G367" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H367" s="1">
         <v>0.15</v>
@@ -17671,7 +17671,7 @@
         <v>70-84</v>
       </c>
       <c r="G368" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H368" s="1">
         <v>0.15</v>
@@ -17718,7 +17718,7 @@
         <v>70-84</v>
       </c>
       <c r="G369" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H369" s="1">
         <v>0.15</v>
@@ -17765,7 +17765,7 @@
         <v>70-84</v>
       </c>
       <c r="G370" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H370" s="1">
         <v>0.15</v>
@@ -17812,7 +17812,7 @@
         <v>70-84</v>
       </c>
       <c r="G371" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H371" s="1">
         <v>0.1</v>
@@ -17859,7 +17859,7 @@
         <v>70-84</v>
       </c>
       <c r="G372" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H372" s="1">
         <v>0.1</v>
@@ -17906,7 +17906,7 @@
         <v>70-84</v>
       </c>
       <c r="G373" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H373" s="1">
         <v>0.1</v>
@@ -17953,7 +17953,7 @@
         <v>70-84</v>
       </c>
       <c r="G374" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H374" s="1">
         <v>0.1</v>
@@ -18000,7 +18000,7 @@
         <v>82-95</v>
       </c>
       <c r="G375" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H375" s="1">
         <v>0.15</v>
@@ -18047,7 +18047,7 @@
         <v>82-95</v>
       </c>
       <c r="G376" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H376" s="1">
         <v>0.15</v>
@@ -18094,7 +18094,7 @@
         <v>82-95</v>
       </c>
       <c r="G377" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H377" s="1">
         <v>0.15</v>
@@ -18141,7 +18141,7 @@
         <v>82-95</v>
       </c>
       <c r="G378" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H378" s="1">
         <v>0.15</v>
@@ -18188,7 +18188,7 @@
         <v>82-95</v>
       </c>
       <c r="G379" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H379" s="1">
         <v>0.1</v>
@@ -18235,7 +18235,7 @@
         <v>82-95</v>
       </c>
       <c r="G380" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H380" s="1">
         <v>0.1</v>
@@ -18282,7 +18282,7 @@
         <v>82-95</v>
       </c>
       <c r="G381" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H381" s="1">
         <v>0.1</v>
@@ -18329,7 +18329,7 @@
         <v>82-95</v>
       </c>
       <c r="G382" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H382" s="1">
         <v>0.05</v>
@@ -18376,7 +18376,7 @@
         <v>82-95</v>
       </c>
       <c r="G383" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H383" s="1">
         <v>0.05</v>
@@ -18423,7 +18423,7 @@
         <v>70-80</v>
       </c>
       <c r="G384" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H384" s="1">
         <v>0.15</v>
@@ -18470,7 +18470,7 @@
         <v>70-80</v>
       </c>
       <c r="G385" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H385" s="1">
         <v>0.15</v>
@@ -18517,7 +18517,7 @@
         <v>70-80</v>
       </c>
       <c r="G386" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H386" s="1">
         <v>0.15</v>
@@ -18564,7 +18564,7 @@
         <v>70-80</v>
       </c>
       <c r="G387" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H387" s="1">
         <v>0.15</v>
@@ -18611,7 +18611,7 @@
         <v>70-80</v>
       </c>
       <c r="G388" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H388" s="1">
         <v>0.1</v>
@@ -18658,7 +18658,7 @@
         <v>70-80</v>
       </c>
       <c r="G389" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H389" s="1">
         <v>0.1</v>
@@ -18705,7 +18705,7 @@
         <v>70-80</v>
       </c>
       <c r="G390" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H390" s="1">
         <v>0.1</v>
@@ -18752,7 +18752,7 @@
         <v>70-80</v>
       </c>
       <c r="G391" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H391" s="1">
         <v>0.05</v>
@@ -18799,7 +18799,7 @@
         <v>70-80</v>
       </c>
       <c r="G392" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H392" s="1">
         <v>0.05</v>
@@ -18846,7 +18846,7 @@
         <v>70-95</v>
       </c>
       <c r="G393" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H393" s="1">
         <v>0.2</v>
@@ -18893,7 +18893,7 @@
         <v>70-95</v>
       </c>
       <c r="G394" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H394" s="1">
         <v>0.15</v>
@@ -18940,7 +18940,7 @@
         <v>70-95</v>
       </c>
       <c r="G395" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H395" s="1">
         <v>0.15</v>
@@ -18987,7 +18987,7 @@
         <v>70-95</v>
       </c>
       <c r="G396" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H396" s="1">
         <v>0.15</v>
@@ -19034,7 +19034,7 @@
         <v>70-95</v>
       </c>
       <c r="G397" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H397" s="1">
         <v>0.15</v>
@@ -19081,7 +19081,7 @@
         <v>70-95</v>
       </c>
       <c r="G398" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H398" s="1">
         <v>0.1</v>
@@ -19128,7 +19128,7 @@
         <v>70-95</v>
       </c>
       <c r="G399" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H399" s="1">
         <v>0.1</v>
@@ -19175,7 +19175,7 @@
         <v>70-75</v>
       </c>
       <c r="G400" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H400" s="1">
         <v>0.2</v>
@@ -19222,7 +19222,7 @@
         <v>70-75</v>
       </c>
       <c r="G401" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H401" s="1">
         <v>0.2</v>
@@ -19269,7 +19269,7 @@
         <v>70-75</v>
       </c>
       <c r="G402" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H402" s="1">
         <v>0.2</v>
@@ -19316,7 +19316,7 @@
         <v>70-75</v>
       </c>
       <c r="G403" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H403" s="1">
         <v>0.15</v>
@@ -19363,7 +19363,7 @@
         <v>70-75</v>
       </c>
       <c r="G404" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H404" s="1">
         <v>0.15</v>
@@ -19410,7 +19410,7 @@
         <v>70-75</v>
       </c>
       <c r="G405" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H405" s="1">
         <v>0.1</v>
@@ -19457,7 +19457,7 @@
         <v>73-79</v>
       </c>
       <c r="G406" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H406" s="1">
         <v>0.15</v>
@@ -19504,7 +19504,7 @@
         <v>73-79</v>
       </c>
       <c r="G407" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H407" s="1">
         <v>0.15</v>
@@ -19551,7 +19551,7 @@
         <v>73-79</v>
       </c>
       <c r="G408" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H408" s="1">
         <v>0.15</v>
@@ -19598,7 +19598,7 @@
         <v>73-79</v>
       </c>
       <c r="G409" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H409" s="1">
         <v>0.15</v>
@@ -19645,7 +19645,7 @@
         <v>73-79</v>
       </c>
       <c r="G410" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H410" s="1">
         <v>0.1</v>
@@ -19692,7 +19692,7 @@
         <v>73-79</v>
       </c>
       <c r="G411" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H411" s="1">
         <v>0.1</v>
@@ -19739,7 +19739,7 @@
         <v>73-79</v>
       </c>
       <c r="G412" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H412" s="1">
         <v>0.1</v>
@@ -19786,7 +19786,7 @@
         <v>73-79</v>
       </c>
       <c r="G413" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H413" s="1">
         <v>0.05</v>
@@ -19833,7 +19833,7 @@
         <v>73-79</v>
       </c>
       <c r="G414" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H414" s="1">
         <v>0.05</v>
@@ -19880,7 +19880,7 @@
         <v>80-86</v>
       </c>
       <c r="G415" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H415" s="1">
         <v>1</v>
@@ -19927,7 +19927,7 @@
         <v>78-88</v>
       </c>
       <c r="G416" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H416" s="1">
         <v>0.15</v>
@@ -19974,7 +19974,7 @@
         <v>78-88</v>
       </c>
       <c r="G417" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H417" s="1">
         <v>0.15</v>
@@ -20021,7 +20021,7 @@
         <v>78-88</v>
       </c>
       <c r="G418" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H418" s="1">
         <v>0.15</v>
@@ -20068,7 +20068,7 @@
         <v>78-88</v>
       </c>
       <c r="G419" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H419" s="1">
         <v>0.15</v>
@@ -20115,7 +20115,7 @@
         <v>78-88</v>
       </c>
       <c r="G420" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H420" s="1">
         <v>0.1</v>
@@ -20162,7 +20162,7 @@
         <v>78-88</v>
       </c>
       <c r="G421" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H421" s="1">
         <v>0.1</v>
@@ -20209,7 +20209,7 @@
         <v>78-88</v>
       </c>
       <c r="G422" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H422" s="1">
         <v>0.1</v>
@@ -20256,7 +20256,7 @@
         <v>78-88</v>
       </c>
       <c r="G423" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H423" s="1">
         <v>0.1</v>
@@ -20303,7 +20303,7 @@
         <v>86-95</v>
       </c>
       <c r="G424" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H424" s="1">
         <v>0.2</v>
@@ -20350,7 +20350,7 @@
         <v>86-95</v>
       </c>
       <c r="G425" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H425" s="1">
         <v>0.15</v>
@@ -20397,7 +20397,7 @@
         <v>86-95</v>
       </c>
       <c r="G426" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H426" s="1">
         <v>0.15</v>
@@ -20444,7 +20444,7 @@
         <v>86-95</v>
       </c>
       <c r="G427" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H427" s="1">
         <v>0.15</v>
@@ -20491,7 +20491,7 @@
         <v>86-95</v>
       </c>
       <c r="G428" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H428" s="1">
         <v>0.15</v>
@@ -20538,7 +20538,7 @@
         <v>86-95</v>
       </c>
       <c r="G429" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H429" s="1">
         <v>0.1</v>
@@ -20585,7 +20585,7 @@
         <v>86-95</v>
       </c>
       <c r="G430" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H430" s="1">
         <v>0.1</v>
@@ -20632,7 +20632,7 @@
         <v>100-100</v>
       </c>
       <c r="G431" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H431" s="1">
         <v>0.5</v>
@@ -20679,7 +20679,7 @@
         <v>100-100</v>
       </c>
       <c r="G432" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H432" s="1">
         <v>0.5</v>
@@ -20726,7 +20726,7 @@
         <v>77-82</v>
       </c>
       <c r="G433" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H433" s="1">
         <v>0.25</v>
@@ -20773,7 +20773,7 @@
         <v>77-82</v>
       </c>
       <c r="G434" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H434" s="1">
         <v>0.25</v>
@@ -20820,7 +20820,7 @@
         <v>77-82</v>
       </c>
       <c r="G435" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H435" s="1">
         <v>0.2</v>
@@ -20867,7 +20867,7 @@
         <v>77-82</v>
       </c>
       <c r="G436" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H436" s="1">
         <v>0.15</v>
@@ -20914,7 +20914,7 @@
         <v>77-82</v>
       </c>
       <c r="G437" t="str">
-        <v>46-51</v>
+        <v>45-49</v>
       </c>
       <c r="H437" s="1">
         <v>0.15</v>
@@ -20961,7 +20961,7 @@
         <v>100-100</v>
       </c>
       <c r="G438" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H438" s="1">
         <v>0.5</v>
@@ -21008,7 +21008,7 @@
         <v>100-100</v>
       </c>
       <c r="G439" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H439" s="1">
         <v>0.5</v>
@@ -21055,7 +21055,7 @@
         <v>100-100</v>
       </c>
       <c r="G440" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H440" s="1">
         <v>0.5</v>
@@ -21102,7 +21102,7 @@
         <v>100-100</v>
       </c>
       <c r="G441" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H441" s="1">
         <v>0.5</v>
@@ -21149,7 +21149,7 @@
         <v>100-100</v>
       </c>
       <c r="G442" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H442" s="1">
         <v>0.5</v>
@@ -21196,7 +21196,7 @@
         <v>100-100</v>
       </c>
       <c r="G443" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H443" s="1">
         <v>0.5</v>
@@ -21243,7 +21243,7 @@
         <v>100-100</v>
       </c>
       <c r="G444" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H444" s="1">
         <v>0.34</v>
@@ -21290,7 +21290,7 @@
         <v>100-100</v>
       </c>
       <c r="G445" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H445" s="1">
         <v>0.33</v>
@@ -21337,7 +21337,7 @@
         <v>100-100</v>
       </c>
       <c r="G446" t="str">
-        <v>46-51</v>
+        <v>96-104</v>
       </c>
       <c r="H446" s="1">
         <v>0.33</v>

--- a/8_Galar_Data.xlsx
+++ b/8_Galar_Data.xlsx
@@ -2114,7 +2114,7 @@
         <v>10-14</v>
       </c>
       <c r="G37" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H37" s="1">
         <v>0.15</v>
@@ -2161,7 +2161,7 @@
         <v>10-14</v>
       </c>
       <c r="G38" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H38" s="1">
         <v>0.15</v>
@@ -2208,7 +2208,7 @@
         <v>10-14</v>
       </c>
       <c r="G39" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H39" s="1">
         <v>0.15</v>
@@ -2255,7 +2255,7 @@
         <v>10-14</v>
       </c>
       <c r="G40" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H40" s="1">
         <v>0.15</v>
@@ -2302,7 +2302,7 @@
         <v>10-14</v>
       </c>
       <c r="G41" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H41" s="1">
         <v>0.1</v>
@@ -2349,7 +2349,7 @@
         <v>10-14</v>
       </c>
       <c r="G42" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H42" s="1">
         <v>0.1</v>
@@ -2396,7 +2396,7 @@
         <v>10-14</v>
       </c>
       <c r="G43" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H43" s="1">
         <v>0.1</v>
@@ -2443,7 +2443,7 @@
         <v>10-14</v>
       </c>
       <c r="G44" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H44" s="1">
         <v>0.05</v>
@@ -2490,7 +2490,7 @@
         <v>10-14</v>
       </c>
       <c r="G45" t="str">
-        <v>3-5</v>
+        <v>4-6</v>
       </c>
       <c r="H45" s="1">
         <v>0.05</v>
@@ -3242,7 +3242,7 @@
         <v>17-21</v>
       </c>
       <c r="G61" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H61" s="1">
         <v>0.15</v>
@@ -3289,7 +3289,7 @@
         <v>17-21</v>
       </c>
       <c r="G62" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H62" s="1">
         <v>0.15</v>
@@ -3336,7 +3336,7 @@
         <v>17-21</v>
       </c>
       <c r="G63" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H63" s="1">
         <v>0.15</v>
@@ -3383,7 +3383,7 @@
         <v>17-21</v>
       </c>
       <c r="G64" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H64" s="1">
         <v>0.15</v>
@@ -3430,7 +3430,7 @@
         <v>17-21</v>
       </c>
       <c r="G65" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H65" s="1">
         <v>0.1</v>
@@ -3477,7 +3477,7 @@
         <v>17-21</v>
       </c>
       <c r="G66" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H66" s="1">
         <v>0.1</v>
@@ -3524,7 +3524,7 @@
         <v>17-21</v>
       </c>
       <c r="G67" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H67" s="1">
         <v>0.1</v>
@@ -3571,7 +3571,7 @@
         <v>17-21</v>
       </c>
       <c r="G68" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H68" s="1">
         <v>0.1</v>
@@ -5451,7 +5451,7 @@
         <v>28-32</v>
       </c>
       <c r="G108" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H108" s="1">
         <v>0.15</v>
@@ -5498,7 +5498,7 @@
         <v>28-32</v>
       </c>
       <c r="G109" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H109" s="1">
         <v>0.15</v>
@@ -5545,7 +5545,7 @@
         <v>28-32</v>
       </c>
       <c r="G110" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H110" s="1">
         <v>0.15</v>
@@ -5592,7 +5592,7 @@
         <v>28-32</v>
       </c>
       <c r="G111" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H111" s="1">
         <v>0.15</v>
@@ -5639,7 +5639,7 @@
         <v>28-32</v>
       </c>
       <c r="G112" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H112" s="1">
         <v>0.1</v>
@@ -5686,7 +5686,7 @@
         <v>28-32</v>
       </c>
       <c r="G113" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H113" s="1">
         <v>0.1</v>
@@ -5733,7 +5733,7 @@
         <v>28-32</v>
       </c>
       <c r="G114" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H114" s="1">
         <v>0.1</v>
@@ -5780,7 +5780,7 @@
         <v>28-32</v>
       </c>
       <c r="G115" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H115" s="1">
         <v>0.05</v>
@@ -5827,7 +5827,7 @@
         <v>28-32</v>
       </c>
       <c r="G116" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H116" s="1">
         <v>0.05</v>
@@ -6626,7 +6626,7 @@
         <v>35-39</v>
       </c>
       <c r="G133" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H133" s="1">
         <v>0.15</v>
@@ -6673,7 +6673,7 @@
         <v>35-39</v>
       </c>
       <c r="G134" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H134" s="1">
         <v>0.15</v>
@@ -6720,7 +6720,7 @@
         <v>35-39</v>
       </c>
       <c r="G135" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H135" s="1">
         <v>0.15</v>
@@ -6767,7 +6767,7 @@
         <v>35-39</v>
       </c>
       <c r="G136" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H136" s="1">
         <v>0.15</v>
@@ -6814,7 +6814,7 @@
         <v>35-39</v>
       </c>
       <c r="G137" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H137" s="1">
         <v>0.1</v>
@@ -6861,7 +6861,7 @@
         <v>35-39</v>
       </c>
       <c r="G138" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H138" s="1">
         <v>0.1</v>
@@ -6908,7 +6908,7 @@
         <v>35-39</v>
       </c>
       <c r="G139" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H139" s="1">
         <v>0.1</v>
@@ -6955,7 +6955,7 @@
         <v>35-39</v>
       </c>
       <c r="G140" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H140" s="1">
         <v>0.1</v>
@@ -7378,7 +7378,7 @@
         <v>40-44</v>
       </c>
       <c r="G149" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H149" s="1">
         <v>0.2</v>
@@ -7425,7 +7425,7 @@
         <v>40-44</v>
       </c>
       <c r="G150" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H150" s="1">
         <v>0.15</v>
@@ -7472,7 +7472,7 @@
         <v>40-44</v>
       </c>
       <c r="G151" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H151" s="1">
         <v>0.15</v>
@@ -7519,7 +7519,7 @@
         <v>40-44</v>
       </c>
       <c r="G152" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H152" s="1">
         <v>0.15</v>
@@ -7566,7 +7566,7 @@
         <v>40-44</v>
       </c>
       <c r="G153" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H153" s="1">
         <v>0.15</v>
@@ -7613,7 +7613,7 @@
         <v>40-44</v>
       </c>
       <c r="G154" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H154" s="1">
         <v>0.1</v>
@@ -7660,7 +7660,7 @@
         <v>40-44</v>
       </c>
       <c r="G155" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H155" s="1">
         <v>0.1</v>
@@ -7707,7 +7707,7 @@
         <v>42-46</v>
       </c>
       <c r="G156" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H156" s="1">
         <v>0.06</v>
@@ -7754,7 +7754,7 @@
         <v>42-46</v>
       </c>
       <c r="G157" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H157" s="1">
         <v>0.06</v>
@@ -7801,7 +7801,7 @@
         <v>42-46</v>
       </c>
       <c r="G158" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H158" s="1">
         <v>0.06</v>
@@ -7848,7 +7848,7 @@
         <v>42-46</v>
       </c>
       <c r="G159" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H159" s="1">
         <v>0.06</v>
@@ -7895,7 +7895,7 @@
         <v>42-46</v>
       </c>
       <c r="G160" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H160" s="1">
         <v>0.06</v>
@@ -7942,7 +7942,7 @@
         <v>42-46</v>
       </c>
       <c r="G161" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H161" s="1">
         <v>0.06</v>
@@ -7989,7 +7989,7 @@
         <v>42-46</v>
       </c>
       <c r="G162" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H162" s="1">
         <v>0.06</v>
@@ -8036,7 +8036,7 @@
         <v>42-46</v>
       </c>
       <c r="G163" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H163" s="1">
         <v>0.06</v>
@@ -8083,7 +8083,7 @@
         <v>42-46</v>
       </c>
       <c r="G164" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H164" s="1">
         <v>0.06</v>
@@ -8130,7 +8130,7 @@
         <v>42-46</v>
       </c>
       <c r="G165" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H165" s="1">
         <v>0.06</v>
@@ -8177,7 +8177,7 @@
         <v>42-46</v>
       </c>
       <c r="G166" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H166" s="1">
         <v>0.06</v>
@@ -8224,7 +8224,7 @@
         <v>42-46</v>
       </c>
       <c r="G167" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H167" s="1">
         <v>0.06</v>
@@ -8271,7 +8271,7 @@
         <v>42-46</v>
       </c>
       <c r="G168" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H168" s="1">
         <v>0.06</v>
@@ -8318,7 +8318,7 @@
         <v>42-46</v>
       </c>
       <c r="G169" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H169" s="1">
         <v>0.06</v>
@@ -8365,7 +8365,7 @@
         <v>42-46</v>
       </c>
       <c r="G170" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H170" s="1">
         <v>0.06</v>
@@ -8412,7 +8412,7 @@
         <v>42-46</v>
       </c>
       <c r="G171" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H171" s="1">
         <v>0.06</v>
@@ -8459,7 +8459,7 @@
         <v>42-46</v>
       </c>
       <c r="G172" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H172" s="1">
         <v>0.05</v>
@@ -8506,7 +8506,7 @@
         <v>42-46</v>
       </c>
       <c r="G173" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H173" s="1">
         <v>0.05</v>
@@ -8553,7 +8553,7 @@
         <v>42-46</v>
       </c>
       <c r="G174" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H174" s="1">
         <v>0.05</v>
@@ -8600,7 +8600,7 @@
         <v>42-46</v>
       </c>
       <c r="G175" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H175" s="1">
         <v>0.05</v>
@@ -9211,7 +9211,7 @@
         <v>47-51</v>
       </c>
       <c r="G188" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H188" s="1">
         <v>0.19</v>
@@ -9258,7 +9258,7 @@
         <v>47-51</v>
       </c>
       <c r="G189" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H189" s="1">
         <v>0.19</v>
@@ -9305,7 +9305,7 @@
         <v>47-51</v>
       </c>
       <c r="G190" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H190" s="1">
         <v>0.19</v>
@@ -9352,7 +9352,7 @@
         <v>47-51</v>
       </c>
       <c r="G191" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H191" s="1">
         <v>0.14</v>
@@ -9399,7 +9399,7 @@
         <v>47-51</v>
       </c>
       <c r="G192" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H192" s="1">
         <v>0.14</v>
@@ -9446,7 +9446,7 @@
         <v>47-51</v>
       </c>
       <c r="G193" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H193" s="1">
         <v>0.1</v>
@@ -9493,7 +9493,7 @@
         <v>47-51</v>
       </c>
       <c r="G194" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H194" s="1">
         <v>0.05</v>
@@ -9540,7 +9540,7 @@
         <v>49-53</v>
       </c>
       <c r="G195" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H195" s="1">
         <v>0.15</v>
@@ -9587,7 +9587,7 @@
         <v>49-53</v>
       </c>
       <c r="G196" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H196" s="1">
         <v>0.15</v>
@@ -9634,7 +9634,7 @@
         <v>49-53</v>
       </c>
       <c r="G197" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H197" s="1">
         <v>0.15</v>
@@ -9681,7 +9681,7 @@
         <v>49-53</v>
       </c>
       <c r="G198" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H198" s="1">
         <v>0.15</v>
@@ -9728,7 +9728,7 @@
         <v>49-53</v>
       </c>
       <c r="G199" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H199" s="1">
         <v>0.1</v>
@@ -9775,7 +9775,7 @@
         <v>49-53</v>
       </c>
       <c r="G200" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H200" s="1">
         <v>0.1</v>
@@ -9822,7 +9822,7 @@
         <v>49-53</v>
       </c>
       <c r="G201" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H201" s="1">
         <v>0.1</v>
@@ -9869,7 +9869,7 @@
         <v>49-53</v>
       </c>
       <c r="G202" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H202" s="1">
         <v>0.1</v>
@@ -9916,7 +9916,7 @@
         <v>51-55</v>
       </c>
       <c r="G203" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H203" s="1">
         <v>0.2</v>
@@ -9963,7 +9963,7 @@
         <v>51-55</v>
       </c>
       <c r="G204" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H204" s="1">
         <v>0.2</v>
@@ -10010,7 +10010,7 @@
         <v>51-55</v>
       </c>
       <c r="G205" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H205" s="1">
         <v>0.2</v>
@@ -10057,7 +10057,7 @@
         <v>51-55</v>
       </c>
       <c r="G206" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H206" s="1">
         <v>0.15</v>
@@ -10104,7 +10104,7 @@
         <v>51-55</v>
       </c>
       <c r="G207" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H207" s="1">
         <v>0.15</v>
@@ -10151,7 +10151,7 @@
         <v>51-55</v>
       </c>
       <c r="G208" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H208" s="1">
         <v>0.1</v>
@@ -10198,7 +10198,7 @@
         <v>53-58</v>
       </c>
       <c r="G209" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H209" s="1">
         <v>0.15</v>
@@ -10245,7 +10245,7 @@
         <v>53-58</v>
       </c>
       <c r="G210" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H210" s="1">
         <v>0.15</v>
@@ -10292,7 +10292,7 @@
         <v>53-58</v>
       </c>
       <c r="G211" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H211" s="1">
         <v>0.15</v>
@@ -10339,7 +10339,7 @@
         <v>53-58</v>
       </c>
       <c r="G212" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H212" s="1">
         <v>0.15</v>
@@ -10386,7 +10386,7 @@
         <v>53-58</v>
       </c>
       <c r="G213" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H213" s="1">
         <v>0.1</v>
@@ -10433,7 +10433,7 @@
         <v>53-58</v>
       </c>
       <c r="G214" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H214" s="1">
         <v>0.1</v>
@@ -10480,7 +10480,7 @@
         <v>53-58</v>
       </c>
       <c r="G215" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H215" s="1">
         <v>0.1</v>
@@ -10527,7 +10527,7 @@
         <v>53-58</v>
       </c>
       <c r="G216" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H216" s="1">
         <v>0.05</v>
@@ -10574,7 +10574,7 @@
         <v>53-58</v>
       </c>
       <c r="G217" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H217" s="1">
         <v>0.05</v>
@@ -10621,7 +10621,7 @@
         <v>56-60</v>
       </c>
       <c r="G218" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H218" s="1">
         <v>0.15</v>
@@ -10668,7 +10668,7 @@
         <v>56-60</v>
       </c>
       <c r="G219" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H219" s="1">
         <v>0.15</v>
@@ -10715,7 +10715,7 @@
         <v>56-60</v>
       </c>
       <c r="G220" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H220" s="1">
         <v>0.15</v>
@@ -10762,7 +10762,7 @@
         <v>56-60</v>
       </c>
       <c r="G221" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H221" s="1">
         <v>0.15</v>
@@ -10809,7 +10809,7 @@
         <v>56-60</v>
       </c>
       <c r="G222" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H222" s="1">
         <v>0.1</v>
@@ -10856,7 +10856,7 @@
         <v>56-60</v>
       </c>
       <c r="G223" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H223" s="1">
         <v>0.1</v>
@@ -10903,7 +10903,7 @@
         <v>56-60</v>
       </c>
       <c r="G224" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H224" s="1">
         <v>0.1</v>
@@ -10950,7 +10950,7 @@
         <v>56-60</v>
       </c>
       <c r="G225" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H225" s="1">
         <v>0.05</v>
@@ -10997,7 +10997,7 @@
         <v>56-60</v>
       </c>
       <c r="G226" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H226" s="1">
         <v>0.05</v>
@@ -11044,7 +11044,7 @@
         <v>58-62</v>
       </c>
       <c r="G227" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H227" s="1">
         <v>0.09</v>
@@ -11091,7 +11091,7 @@
         <v>58-62</v>
       </c>
       <c r="G228" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H228" s="1">
         <v>0.09</v>
@@ -11138,7 +11138,7 @@
         <v>58-62</v>
       </c>
       <c r="G229" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H229" s="1">
         <v>0.09</v>
@@ -11185,7 +11185,7 @@
         <v>58-62</v>
       </c>
       <c r="G230" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H230" s="1">
         <v>0.09</v>
@@ -11232,7 +11232,7 @@
         <v>58-62</v>
       </c>
       <c r="G231" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H231" s="1">
         <v>0.09</v>
@@ -11279,7 +11279,7 @@
         <v>58-62</v>
       </c>
       <c r="G232" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H232" s="1">
         <v>0.09</v>
@@ -11326,7 +11326,7 @@
         <v>58-62</v>
       </c>
       <c r="G233" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H233" s="1">
         <v>0.09</v>
@@ -11373,7 +11373,7 @@
         <v>58-62</v>
       </c>
       <c r="G234" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H234" s="1">
         <v>0.09</v>
@@ -11420,7 +11420,7 @@
         <v>58-62</v>
       </c>
       <c r="G235" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H235" s="1">
         <v>0.09</v>
@@ -11467,7 +11467,7 @@
         <v>58-62</v>
       </c>
       <c r="G236" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H236" s="1">
         <v>0.09</v>
@@ -11514,7 +11514,7 @@
         <v>58-62</v>
       </c>
       <c r="G237" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H237" s="1">
         <v>0.09</v>
@@ -11561,7 +11561,7 @@
         <v>60-65</v>
       </c>
       <c r="G238" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H238" s="1">
         <v>0.07</v>
@@ -11608,7 +11608,7 @@
         <v>60-65</v>
       </c>
       <c r="G239" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H239" s="1">
         <v>0.07</v>
@@ -11655,7 +11655,7 @@
         <v>60-65</v>
       </c>
       <c r="G240" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H240" s="1">
         <v>0.07</v>
@@ -11702,7 +11702,7 @@
         <v>60-65</v>
       </c>
       <c r="G241" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H241" s="1">
         <v>0.07</v>
@@ -11749,7 +11749,7 @@
         <v>60-65</v>
       </c>
       <c r="G242" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H242" s="1">
         <v>0.07</v>
@@ -11796,7 +11796,7 @@
         <v>60-65</v>
       </c>
       <c r="G243" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H243" s="1">
         <v>0.07</v>
@@ -11843,7 +11843,7 @@
         <v>60-65</v>
       </c>
       <c r="G244" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H244" s="1">
         <v>0.07</v>
@@ -11890,7 +11890,7 @@
         <v>60-65</v>
       </c>
       <c r="G245" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H245" s="1">
         <v>0.07</v>
@@ -11937,7 +11937,7 @@
         <v>60-65</v>
       </c>
       <c r="G246" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H246" s="1">
         <v>0.07</v>
@@ -11984,7 +11984,7 @@
         <v>60-65</v>
       </c>
       <c r="G247" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H247" s="1">
         <v>0.07</v>
@@ -12031,7 +12031,7 @@
         <v>60-65</v>
       </c>
       <c r="G248" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H248" s="1">
         <v>0.07</v>
@@ -12078,7 +12078,7 @@
         <v>60-65</v>
       </c>
       <c r="G249" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H249" s="1">
         <v>0.07</v>
@@ -12125,7 +12125,7 @@
         <v>60-65</v>
       </c>
       <c r="G250" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H250" s="1">
         <v>0.07</v>
@@ -12172,7 +12172,7 @@
         <v>60-65</v>
       </c>
       <c r="G251" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H251" s="1">
         <v>0.07</v>
@@ -12689,7 +12689,7 @@
         <v>65-69</v>
       </c>
       <c r="G262" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H262" s="1">
         <v>0.15</v>
@@ -12736,7 +12736,7 @@
         <v>65-69</v>
       </c>
       <c r="G263" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H263" s="1">
         <v>0.15</v>
@@ -12783,7 +12783,7 @@
         <v>65-69</v>
       </c>
       <c r="G264" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H264" s="1">
         <v>0.15</v>
@@ -12830,7 +12830,7 @@
         <v>65-69</v>
       </c>
       <c r="G265" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H265" s="1">
         <v>0.15</v>
@@ -12877,7 +12877,7 @@
         <v>65-69</v>
       </c>
       <c r="G266" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H266" s="1">
         <v>0.1</v>
@@ -12924,7 +12924,7 @@
         <v>65-69</v>
       </c>
       <c r="G267" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H267" s="1">
         <v>0.1</v>
@@ -12971,7 +12971,7 @@
         <v>65-69</v>
       </c>
       <c r="G268" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H268" s="1">
         <v>0.1</v>
@@ -13018,7 +13018,7 @@
         <v>65-69</v>
       </c>
       <c r="G269" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H269" s="1">
         <v>0.05</v>
@@ -13065,7 +13065,7 @@
         <v>65-69</v>
       </c>
       <c r="G270" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H270" s="1">
         <v>0.05</v>
@@ -13112,7 +13112,7 @@
         <v>65-69</v>
       </c>
       <c r="G271" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H271" s="1">
         <v>0.05</v>
@@ -13300,7 +13300,7 @@
         <v>67-70</v>
       </c>
       <c r="G275" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H275" s="1">
         <v>0.15</v>
@@ -13347,7 +13347,7 @@
         <v>67-70</v>
       </c>
       <c r="G276" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H276" s="1">
         <v>0.15</v>
@@ -13394,7 +13394,7 @@
         <v>67-70</v>
       </c>
       <c r="G277" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H277" s="1">
         <v>0.15</v>
@@ -13441,7 +13441,7 @@
         <v>67-70</v>
       </c>
       <c r="G278" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H278" s="1">
         <v>0.15</v>
@@ -13488,7 +13488,7 @@
         <v>67-70</v>
       </c>
       <c r="G279" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H279" s="1">
         <v>0.1</v>
@@ -13535,7 +13535,7 @@
         <v>67-70</v>
       </c>
       <c r="G280" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H280" s="1">
         <v>0.1</v>
@@ -13582,7 +13582,7 @@
         <v>67-70</v>
       </c>
       <c r="G281" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H281" s="1">
         <v>0.1</v>
@@ -13629,7 +13629,7 @@
         <v>67-70</v>
       </c>
       <c r="G282" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H282" s="1">
         <v>0.05</v>
@@ -13676,7 +13676,7 @@
         <v>67-70</v>
       </c>
       <c r="G283" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H283" s="1">
         <v>0.05</v>
@@ -13723,7 +13723,7 @@
         <v>67-70</v>
       </c>
       <c r="G284" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H284" s="1">
         <v>0.05</v>
@@ -13911,7 +13911,7 @@
         <v>70-70</v>
       </c>
       <c r="G288" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H288" s="1">
         <v>0.14</v>
@@ -13958,7 +13958,7 @@
         <v>70-70</v>
       </c>
       <c r="G289" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H289" s="1">
         <v>0.14</v>
@@ -14005,7 +14005,7 @@
         <v>70-70</v>
       </c>
       <c r="G290" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H290" s="1">
         <v>0.14</v>
@@ -14052,7 +14052,7 @@
         <v>70-70</v>
       </c>
       <c r="G291" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H291" s="1">
         <v>0.14</v>
@@ -14099,7 +14099,7 @@
         <v>70-70</v>
       </c>
       <c r="G292" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H292" s="1">
         <v>0.1</v>
@@ -14146,7 +14146,7 @@
         <v>70-70</v>
       </c>
       <c r="G293" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H293" s="1">
         <v>0.1</v>
@@ -14193,7 +14193,7 @@
         <v>70-70</v>
       </c>
       <c r="G294" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H294" s="1">
         <v>0.1</v>
@@ -14240,7 +14240,7 @@
         <v>70-70</v>
       </c>
       <c r="G295" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H295" s="1">
         <v>0.05</v>
@@ -14287,7 +14287,7 @@
         <v>70-70</v>
       </c>
       <c r="G296" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H296" s="1">
         <v>0.05</v>
@@ -14334,7 +14334,7 @@
         <v>70-70</v>
       </c>
       <c r="G297" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H297" s="1">
         <v>0.05</v>
@@ -16214,7 +16214,7 @@
         <v>30-30</v>
       </c>
       <c r="G337" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H337" s="1">
         <v>1</v>
@@ -17342,7 +17342,7 @@
         <v>55-55</v>
       </c>
       <c r="G361" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H361" s="1">
         <v>0.25</v>
@@ -17389,7 +17389,7 @@
         <v>55-55</v>
       </c>
       <c r="G362" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H362" s="1">
         <v>0.25</v>
@@ -17436,7 +17436,7 @@
         <v>55-55</v>
       </c>
       <c r="G363" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H363" s="1">
         <v>0.2</v>
@@ -17483,7 +17483,7 @@
         <v>55-55</v>
       </c>
       <c r="G364" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H364" s="1">
         <v>0.15</v>
@@ -17530,7 +17530,7 @@
         <v>55-55</v>
       </c>
       <c r="G365" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H365" s="1">
         <v>0.15</v>
@@ -18611,7 +18611,7 @@
         <v>100-100</v>
       </c>
       <c r="G388" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H388" s="1">
         <v>0.5</v>
@@ -18658,7 +18658,7 @@
         <v>100-100</v>
       </c>
       <c r="G389" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H389" s="1">
         <v>0.5</v>
@@ -18846,7 +18846,7 @@
         <v>100-100</v>
       </c>
       <c r="G393" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H393" s="1">
         <v>0.5</v>
@@ -18893,7 +18893,7 @@
         <v>100-100</v>
       </c>
       <c r="G394" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H394" s="1">
         <v>0.5</v>
@@ -22183,7 +22183,7 @@
         <v>100-100</v>
       </c>
       <c r="G464" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H464" s="1">
         <v>0.5</v>
@@ -22230,7 +22230,7 @@
         <v>100-100</v>
       </c>
       <c r="G465" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H465" s="1">
         <v>0.5</v>
